--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,3002 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121562390</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>416139</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047589</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121562407</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>416664</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047789</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121562379</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>416590</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121562396</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416304</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047548</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121562398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>416421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7047618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121562389</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>416120</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7047580</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121562406</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>416562</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7047700</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121562404</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>416533</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7047678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121562393</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416175</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7047616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121562381</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>416464</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7047388</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121562400</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>416426</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7047612</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121562401</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>416440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7047666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121562380</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>416570</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7047580</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121562386</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>416228</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7047510</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121562397</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>416318</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7047519</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121562403</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>416432</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7047696</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121562394</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>416218</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7047582</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121562385</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>416229</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7047508</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121562388</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>416185</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7047533</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121562384</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>416263</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7047490</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121562395</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>416317</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7047574</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121562405</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>416545</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7047634</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121562383</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>416419</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7047402</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121562387</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>416169</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7047551</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121562391</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>416161</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7047590</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121562402</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>416433</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7047695</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121562392</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>416156</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7047605</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121562382</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>416431</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7047412</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562390</v>
+        <v>121562404</v>
       </c>
       <c r="B3" t="n">
         <v>57355</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416139</v>
+        <v>416533</v>
       </c>
       <c r="R3" t="n">
-        <v>7047589</v>
+        <v>7047678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562407</v>
+        <v>121562384</v>
       </c>
       <c r="B4" t="n">
         <v>57355</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416664</v>
+        <v>416263</v>
       </c>
       <c r="R4" t="n">
-        <v>7047789</v>
+        <v>7047490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562379</v>
+        <v>121562403</v>
       </c>
       <c r="B5" t="n">
         <v>57355</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416590</v>
+        <v>416432</v>
       </c>
       <c r="R5" t="n">
-        <v>7047648</v>
+        <v>7047696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562396</v>
+        <v>121562388</v>
       </c>
       <c r="B6" t="n">
         <v>57355</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416304</v>
+        <v>416185</v>
       </c>
       <c r="R6" t="n">
-        <v>7047548</v>
+        <v>7047533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562398</v>
+        <v>121562389</v>
       </c>
       <c r="B7" t="n">
         <v>57355</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416421</v>
+        <v>416120</v>
       </c>
       <c r="R7" t="n">
-        <v>7047618</v>
+        <v>7047580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562389</v>
+        <v>121562398</v>
       </c>
       <c r="B8" t="n">
         <v>57355</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416120</v>
+        <v>416421</v>
       </c>
       <c r="R8" t="n">
-        <v>7047580</v>
+        <v>7047618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562406</v>
+        <v>121562391</v>
       </c>
       <c r="B9" t="n">
         <v>57355</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416562</v>
+        <v>416161</v>
       </c>
       <c r="R9" t="n">
-        <v>7047700</v>
+        <v>7047590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562404</v>
+        <v>121562393</v>
       </c>
       <c r="B10" t="n">
         <v>57355</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416533</v>
+        <v>416175</v>
       </c>
       <c r="R10" t="n">
-        <v>7047678</v>
+        <v>7047616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562393</v>
+        <v>121562397</v>
       </c>
       <c r="B11" t="n">
         <v>57355</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416175</v>
+        <v>416318</v>
       </c>
       <c r="R11" t="n">
-        <v>7047616</v>
+        <v>7047519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562381</v>
+        <v>121562396</v>
       </c>
       <c r="B12" t="n">
         <v>57355</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416464</v>
+        <v>416304</v>
       </c>
       <c r="R12" t="n">
-        <v>7047388</v>
+        <v>7047548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562400</v>
+        <v>121562382</v>
       </c>
       <c r="B13" t="n">
         <v>57355</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416426</v>
+        <v>416431</v>
       </c>
       <c r="R13" t="n">
-        <v>7047612</v>
+        <v>7047412</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562401</v>
+        <v>121562390</v>
       </c>
       <c r="B14" t="n">
         <v>57355</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416440</v>
+        <v>416139</v>
       </c>
       <c r="R14" t="n">
-        <v>7047666</v>
+        <v>7047589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562380</v>
+        <v>121562386</v>
       </c>
       <c r="B15" t="n">
         <v>57355</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416570</v>
+        <v>416228</v>
       </c>
       <c r="R15" t="n">
-        <v>7047580</v>
+        <v>7047510</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562386</v>
+        <v>121562395</v>
       </c>
       <c r="B16" t="n">
         <v>57355</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416228</v>
+        <v>416317</v>
       </c>
       <c r="R16" t="n">
-        <v>7047510</v>
+        <v>7047574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562397</v>
+        <v>121562394</v>
       </c>
       <c r="B17" t="n">
         <v>57355</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416318</v>
+        <v>416218</v>
       </c>
       <c r="R17" t="n">
-        <v>7047519</v>
+        <v>7047582</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562403</v>
+        <v>121562387</v>
       </c>
       <c r="B18" t="n">
         <v>57355</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416432</v>
+        <v>416169</v>
       </c>
       <c r="R18" t="n">
-        <v>7047696</v>
+        <v>7047551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562394</v>
+        <v>121562400</v>
       </c>
       <c r="B19" t="n">
         <v>57355</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416218</v>
+        <v>416426</v>
       </c>
       <c r="R19" t="n">
-        <v>7047582</v>
+        <v>7047612</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562385</v>
+        <v>121562392</v>
       </c>
       <c r="B20" t="n">
         <v>57355</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416229</v>
+        <v>416156</v>
       </c>
       <c r="R20" t="n">
-        <v>7047508</v>
+        <v>7047605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562388</v>
+        <v>121562379</v>
       </c>
       <c r="B21" t="n">
         <v>57355</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416185</v>
+        <v>416590</v>
       </c>
       <c r="R21" t="n">
-        <v>7047533</v>
+        <v>7047648</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562384</v>
+        <v>121562407</v>
       </c>
       <c r="B22" t="n">
         <v>57355</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416263</v>
+        <v>416664</v>
       </c>
       <c r="R22" t="n">
-        <v>7047490</v>
+        <v>7047789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562395</v>
+        <v>121562405</v>
       </c>
       <c r="B23" t="n">
         <v>57355</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416317</v>
+        <v>416545</v>
       </c>
       <c r="R23" t="n">
-        <v>7047574</v>
+        <v>7047634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562405</v>
+        <v>121562401</v>
       </c>
       <c r="B24" t="n">
         <v>57355</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416545</v>
+        <v>416440</v>
       </c>
       <c r="R24" t="n">
-        <v>7047634</v>
+        <v>7047666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562383</v>
+        <v>121562402</v>
       </c>
       <c r="B25" t="n">
         <v>57355</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416419</v>
+        <v>416433</v>
       </c>
       <c r="R25" t="n">
-        <v>7047402</v>
+        <v>7047695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562387</v>
+        <v>121562385</v>
       </c>
       <c r="B26" t="n">
         <v>57355</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416169</v>
+        <v>416229</v>
       </c>
       <c r="R26" t="n">
-        <v>7047551</v>
+        <v>7047508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562391</v>
+        <v>121562380</v>
       </c>
       <c r="B27" t="n">
         <v>57355</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416161</v>
+        <v>416570</v>
       </c>
       <c r="R27" t="n">
-        <v>7047590</v>
+        <v>7047580</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562402</v>
+        <v>121562383</v>
       </c>
       <c r="B28" t="n">
         <v>57355</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416433</v>
+        <v>416419</v>
       </c>
       <c r="R28" t="n">
-        <v>7047695</v>
+        <v>7047402</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562392</v>
+        <v>121562406</v>
       </c>
       <c r="B29" t="n">
         <v>57355</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416156</v>
+        <v>416562</v>
       </c>
       <c r="R29" t="n">
-        <v>7047605</v>
+        <v>7047700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562382</v>
+        <v>121562381</v>
       </c>
       <c r="B30" t="n">
         <v>57355</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416431</v>
+        <v>416464</v>
       </c>
       <c r="R30" t="n">
-        <v>7047412</v>
+        <v>7047388</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562404</v>
+        <v>121562400</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416533</v>
+        <v>416426</v>
       </c>
       <c r="R3" t="n">
-        <v>7047678</v>
+        <v>7047612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562384</v>
+        <v>121562395</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416263</v>
+        <v>416317</v>
       </c>
       <c r="R4" t="n">
-        <v>7047490</v>
+        <v>7047574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562403</v>
+        <v>121562406</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416432</v>
+        <v>416562</v>
       </c>
       <c r="R5" t="n">
-        <v>7047696</v>
+        <v>7047700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562388</v>
+        <v>121562383</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416185</v>
+        <v>416419</v>
       </c>
       <c r="R6" t="n">
-        <v>7047533</v>
+        <v>7047402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562389</v>
+        <v>121562397</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416120</v>
+        <v>416318</v>
       </c>
       <c r="R7" t="n">
-        <v>7047580</v>
+        <v>7047519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562398</v>
+        <v>121562379</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416421</v>
+        <v>416590</v>
       </c>
       <c r="R8" t="n">
-        <v>7047618</v>
+        <v>7047648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562391</v>
+        <v>121562380</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416161</v>
+        <v>416570</v>
       </c>
       <c r="R9" t="n">
-        <v>7047590</v>
+        <v>7047580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562393</v>
+        <v>121562387</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416175</v>
+        <v>416169</v>
       </c>
       <c r="R10" t="n">
-        <v>7047616</v>
+        <v>7047551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562397</v>
+        <v>121562382</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416318</v>
+        <v>416431</v>
       </c>
       <c r="R11" t="n">
-        <v>7047519</v>
+        <v>7047412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562396</v>
+        <v>121562385</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416304</v>
+        <v>416229</v>
       </c>
       <c r="R12" t="n">
-        <v>7047548</v>
+        <v>7047508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562382</v>
+        <v>121562405</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416431</v>
+        <v>416545</v>
       </c>
       <c r="R13" t="n">
-        <v>7047412</v>
+        <v>7047634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562390</v>
+        <v>121562407</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416139</v>
+        <v>416664</v>
       </c>
       <c r="R14" t="n">
-        <v>7047589</v>
+        <v>7047789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562386</v>
+        <v>121562396</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416228</v>
+        <v>416304</v>
       </c>
       <c r="R15" t="n">
-        <v>7047510</v>
+        <v>7047548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562395</v>
+        <v>121562394</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416317</v>
+        <v>416218</v>
       </c>
       <c r="R16" t="n">
-        <v>7047574</v>
+        <v>7047582</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562394</v>
+        <v>121562384</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416218</v>
+        <v>416263</v>
       </c>
       <c r="R17" t="n">
-        <v>7047582</v>
+        <v>7047490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562387</v>
+        <v>121562392</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416169</v>
+        <v>416156</v>
       </c>
       <c r="R18" t="n">
-        <v>7047551</v>
+        <v>7047605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562400</v>
+        <v>121562388</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416426</v>
+        <v>416185</v>
       </c>
       <c r="R19" t="n">
-        <v>7047612</v>
+        <v>7047533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562392</v>
+        <v>121562398</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416156</v>
+        <v>416421</v>
       </c>
       <c r="R20" t="n">
-        <v>7047605</v>
+        <v>7047618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562379</v>
+        <v>121562391</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416590</v>
+        <v>416161</v>
       </c>
       <c r="R21" t="n">
-        <v>7047648</v>
+        <v>7047590</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562407</v>
+        <v>121562386</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416664</v>
+        <v>416228</v>
       </c>
       <c r="R22" t="n">
-        <v>7047789</v>
+        <v>7047510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562405</v>
+        <v>121562381</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416545</v>
+        <v>416464</v>
       </c>
       <c r="R23" t="n">
-        <v>7047634</v>
+        <v>7047388</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562401</v>
+        <v>121562389</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416440</v>
+        <v>416120</v>
       </c>
       <c r="R24" t="n">
-        <v>7047666</v>
+        <v>7047580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562402</v>
+        <v>121562393</v>
       </c>
       <c r="B25" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416433</v>
+        <v>416175</v>
       </c>
       <c r="R25" t="n">
-        <v>7047695</v>
+        <v>7047616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562385</v>
+        <v>121562402</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416229</v>
+        <v>416433</v>
       </c>
       <c r="R26" t="n">
-        <v>7047508</v>
+        <v>7047695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562380</v>
+        <v>121562403</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416570</v>
+        <v>416432</v>
       </c>
       <c r="R27" t="n">
-        <v>7047580</v>
+        <v>7047696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562383</v>
+        <v>121562404</v>
       </c>
       <c r="B28" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416419</v>
+        <v>416533</v>
       </c>
       <c r="R28" t="n">
-        <v>7047402</v>
+        <v>7047678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562406</v>
+        <v>121562401</v>
       </c>
       <c r="B29" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416562</v>
+        <v>416440</v>
       </c>
       <c r="R29" t="n">
-        <v>7047700</v>
+        <v>7047666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562381</v>
+        <v>121562390</v>
       </c>
       <c r="B30" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416464</v>
+        <v>416139</v>
       </c>
       <c r="R30" t="n">
-        <v>7047388</v>
+        <v>7047589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562400</v>
+        <v>121562390</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416426</v>
+        <v>416139</v>
       </c>
       <c r="R3" t="n">
-        <v>7047612</v>
+        <v>7047589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562395</v>
+        <v>121562379</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416317</v>
+        <v>416590</v>
       </c>
       <c r="R4" t="n">
-        <v>7047574</v>
+        <v>7047648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562406</v>
+        <v>121562405</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416562</v>
+        <v>416545</v>
       </c>
       <c r="R5" t="n">
-        <v>7047700</v>
+        <v>7047634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562383</v>
+        <v>121562392</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416419</v>
+        <v>416156</v>
       </c>
       <c r="R6" t="n">
-        <v>7047402</v>
+        <v>7047605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562397</v>
+        <v>121562388</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416318</v>
+        <v>416185</v>
       </c>
       <c r="R7" t="n">
-        <v>7047519</v>
+        <v>7047533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562379</v>
+        <v>121562384</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416590</v>
+        <v>416263</v>
       </c>
       <c r="R8" t="n">
-        <v>7047648</v>
+        <v>7047490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562380</v>
+        <v>121562383</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416570</v>
+        <v>416419</v>
       </c>
       <c r="R9" t="n">
-        <v>7047580</v>
+        <v>7047402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562387</v>
+        <v>121562382</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416169</v>
+        <v>416431</v>
       </c>
       <c r="R10" t="n">
-        <v>7047551</v>
+        <v>7047412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562382</v>
+        <v>121562407</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416431</v>
+        <v>416664</v>
       </c>
       <c r="R11" t="n">
-        <v>7047412</v>
+        <v>7047789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562385</v>
+        <v>121562381</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416229</v>
+        <v>416464</v>
       </c>
       <c r="R12" t="n">
-        <v>7047508</v>
+        <v>7047388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562405</v>
+        <v>121562395</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416545</v>
+        <v>416317</v>
       </c>
       <c r="R13" t="n">
-        <v>7047634</v>
+        <v>7047574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562407</v>
+        <v>121562385</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416664</v>
+        <v>416229</v>
       </c>
       <c r="R14" t="n">
-        <v>7047789</v>
+        <v>7047508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562396</v>
+        <v>121562400</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416304</v>
+        <v>416426</v>
       </c>
       <c r="R15" t="n">
-        <v>7047548</v>
+        <v>7047612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562394</v>
+        <v>121562403</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416218</v>
+        <v>416432</v>
       </c>
       <c r="R16" t="n">
-        <v>7047582</v>
+        <v>7047696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562384</v>
+        <v>121562391</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416263</v>
+        <v>416161</v>
       </c>
       <c r="R17" t="n">
-        <v>7047490</v>
+        <v>7047590</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562392</v>
+        <v>121562387</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416156</v>
+        <v>416169</v>
       </c>
       <c r="R18" t="n">
-        <v>7047605</v>
+        <v>7047551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562388</v>
+        <v>121562401</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416185</v>
+        <v>416440</v>
       </c>
       <c r="R19" t="n">
-        <v>7047533</v>
+        <v>7047666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562398</v>
+        <v>121562397</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416421</v>
+        <v>416318</v>
       </c>
       <c r="R20" t="n">
-        <v>7047618</v>
+        <v>7047519</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562391</v>
+        <v>121562386</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416161</v>
+        <v>416228</v>
       </c>
       <c r="R21" t="n">
-        <v>7047590</v>
+        <v>7047510</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562386</v>
+        <v>121562393</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416228</v>
+        <v>416175</v>
       </c>
       <c r="R22" t="n">
-        <v>7047510</v>
+        <v>7047616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562381</v>
+        <v>121562396</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416464</v>
+        <v>416304</v>
       </c>
       <c r="R23" t="n">
-        <v>7047388</v>
+        <v>7047548</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562389</v>
+        <v>121562402</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416120</v>
+        <v>416433</v>
       </c>
       <c r="R24" t="n">
-        <v>7047580</v>
+        <v>7047695</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562393</v>
+        <v>121562389</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416175</v>
+        <v>416120</v>
       </c>
       <c r="R25" t="n">
-        <v>7047616</v>
+        <v>7047580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562402</v>
+        <v>121562394</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416433</v>
+        <v>416218</v>
       </c>
       <c r="R26" t="n">
-        <v>7047695</v>
+        <v>7047582</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562403</v>
+        <v>121562404</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416432</v>
+        <v>416533</v>
       </c>
       <c r="R27" t="n">
-        <v>7047696</v>
+        <v>7047678</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562404</v>
+        <v>121562398</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416533</v>
+        <v>416421</v>
       </c>
       <c r="R28" t="n">
-        <v>7047678</v>
+        <v>7047618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562401</v>
+        <v>121562380</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416440</v>
+        <v>416570</v>
       </c>
       <c r="R29" t="n">
-        <v>7047666</v>
+        <v>7047580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562390</v>
+        <v>121562406</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416139</v>
+        <v>416562</v>
       </c>
       <c r="R30" t="n">
-        <v>7047589</v>
+        <v>7047700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562390</v>
+        <v>121562402</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416139</v>
+        <v>416433</v>
       </c>
       <c r="R3" t="n">
-        <v>7047589</v>
+        <v>7047695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562379</v>
+        <v>121562397</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416590</v>
+        <v>416318</v>
       </c>
       <c r="R4" t="n">
-        <v>7047648</v>
+        <v>7047519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562405</v>
+        <v>121562393</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416545</v>
+        <v>416175</v>
       </c>
       <c r="R5" t="n">
-        <v>7047634</v>
+        <v>7047616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562392</v>
+        <v>121562395</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416156</v>
+        <v>416317</v>
       </c>
       <c r="R6" t="n">
-        <v>7047605</v>
+        <v>7047574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562388</v>
+        <v>121562391</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416185</v>
+        <v>416161</v>
       </c>
       <c r="R7" t="n">
-        <v>7047533</v>
+        <v>7047590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562384</v>
+        <v>121562383</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416263</v>
+        <v>416419</v>
       </c>
       <c r="R8" t="n">
-        <v>7047490</v>
+        <v>7047402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562383</v>
+        <v>121562392</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416419</v>
+        <v>416156</v>
       </c>
       <c r="R9" t="n">
-        <v>7047402</v>
+        <v>7047605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562382</v>
+        <v>121562380</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416431</v>
+        <v>416570</v>
       </c>
       <c r="R10" t="n">
-        <v>7047412</v>
+        <v>7047580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562407</v>
+        <v>121562386</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416664</v>
+        <v>416228</v>
       </c>
       <c r="R11" t="n">
-        <v>7047789</v>
+        <v>7047510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562381</v>
+        <v>121562401</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416464</v>
+        <v>416440</v>
       </c>
       <c r="R12" t="n">
-        <v>7047388</v>
+        <v>7047666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562395</v>
+        <v>121562407</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416317</v>
+        <v>416664</v>
       </c>
       <c r="R13" t="n">
-        <v>7047574</v>
+        <v>7047789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562385</v>
+        <v>121562387</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416229</v>
+        <v>416169</v>
       </c>
       <c r="R14" t="n">
-        <v>7047508</v>
+        <v>7047551</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562400</v>
+        <v>121562403</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416426</v>
+        <v>416432</v>
       </c>
       <c r="R15" t="n">
-        <v>7047612</v>
+        <v>7047696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562403</v>
+        <v>121562379</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416432</v>
+        <v>416590</v>
       </c>
       <c r="R16" t="n">
-        <v>7047696</v>
+        <v>7047648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562391</v>
+        <v>121562385</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416161</v>
+        <v>416229</v>
       </c>
       <c r="R17" t="n">
-        <v>7047590</v>
+        <v>7047508</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562387</v>
+        <v>121562405</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416169</v>
+        <v>416545</v>
       </c>
       <c r="R18" t="n">
-        <v>7047551</v>
+        <v>7047634</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562401</v>
+        <v>121562394</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416440</v>
+        <v>416218</v>
       </c>
       <c r="R19" t="n">
-        <v>7047666</v>
+        <v>7047582</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562397</v>
+        <v>121562384</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416318</v>
+        <v>416263</v>
       </c>
       <c r="R20" t="n">
-        <v>7047519</v>
+        <v>7047490</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562386</v>
+        <v>121562400</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416228</v>
+        <v>416426</v>
       </c>
       <c r="R21" t="n">
-        <v>7047510</v>
+        <v>7047612</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562393</v>
+        <v>121562406</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416175</v>
+        <v>416562</v>
       </c>
       <c r="R22" t="n">
-        <v>7047616</v>
+        <v>7047700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562396</v>
+        <v>121562382</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416304</v>
+        <v>416431</v>
       </c>
       <c r="R23" t="n">
-        <v>7047548</v>
+        <v>7047412</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562402</v>
+        <v>121562404</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416433</v>
+        <v>416533</v>
       </c>
       <c r="R24" t="n">
-        <v>7047695</v>
+        <v>7047678</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562389</v>
+        <v>121562398</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416120</v>
+        <v>416421</v>
       </c>
       <c r="R25" t="n">
-        <v>7047580</v>
+        <v>7047618</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562394</v>
+        <v>121562390</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416218</v>
+        <v>416139</v>
       </c>
       <c r="R26" t="n">
-        <v>7047582</v>
+        <v>7047589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562404</v>
+        <v>121562396</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416533</v>
+        <v>416304</v>
       </c>
       <c r="R27" t="n">
-        <v>7047678</v>
+        <v>7047548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562398</v>
+        <v>121562381</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416421</v>
+        <v>416464</v>
       </c>
       <c r="R28" t="n">
-        <v>7047618</v>
+        <v>7047388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562380</v>
+        <v>121562388</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416570</v>
+        <v>416185</v>
       </c>
       <c r="R29" t="n">
-        <v>7047580</v>
+        <v>7047533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562406</v>
+        <v>121562389</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416562</v>
+        <v>416120</v>
       </c>
       <c r="R30" t="n">
-        <v>7047700</v>
+        <v>7047580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562402</v>
+        <v>121562397</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416433</v>
+        <v>416318</v>
       </c>
       <c r="R3" t="n">
-        <v>7047695</v>
+        <v>7047519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562397</v>
+        <v>121562396</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416318</v>
+        <v>416304</v>
       </c>
       <c r="R4" t="n">
-        <v>7047519</v>
+        <v>7047548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562393</v>
+        <v>121562394</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416175</v>
+        <v>416218</v>
       </c>
       <c r="R5" t="n">
-        <v>7047616</v>
+        <v>7047582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562395</v>
+        <v>121562386</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416317</v>
+        <v>416228</v>
       </c>
       <c r="R6" t="n">
-        <v>7047574</v>
+        <v>7047510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562391</v>
+        <v>121562387</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416161</v>
+        <v>416169</v>
       </c>
       <c r="R7" t="n">
-        <v>7047590</v>
+        <v>7047551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562383</v>
+        <v>121562388</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416419</v>
+        <v>416185</v>
       </c>
       <c r="R8" t="n">
-        <v>7047402</v>
+        <v>7047533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562392</v>
+        <v>121562402</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416156</v>
+        <v>416433</v>
       </c>
       <c r="R9" t="n">
-        <v>7047605</v>
+        <v>7047695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562380</v>
+        <v>121562391</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416570</v>
+        <v>416161</v>
       </c>
       <c r="R10" t="n">
-        <v>7047580</v>
+        <v>7047590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562386</v>
+        <v>121562401</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416228</v>
+        <v>416440</v>
       </c>
       <c r="R11" t="n">
-        <v>7047510</v>
+        <v>7047666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562401</v>
+        <v>121562382</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416440</v>
+        <v>416431</v>
       </c>
       <c r="R12" t="n">
-        <v>7047666</v>
+        <v>7047412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562407</v>
+        <v>121562398</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416664</v>
+        <v>416421</v>
       </c>
       <c r="R13" t="n">
-        <v>7047789</v>
+        <v>7047618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562387</v>
+        <v>121562405</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416169</v>
+        <v>416545</v>
       </c>
       <c r="R14" t="n">
-        <v>7047551</v>
+        <v>7047634</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562403</v>
+        <v>121562390</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416432</v>
+        <v>416139</v>
       </c>
       <c r="R15" t="n">
-        <v>7047696</v>
+        <v>7047589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562385</v>
+        <v>121562393</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416229</v>
+        <v>416175</v>
       </c>
       <c r="R17" t="n">
-        <v>7047508</v>
+        <v>7047616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562405</v>
+        <v>121562395</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416545</v>
+        <v>416317</v>
       </c>
       <c r="R18" t="n">
-        <v>7047634</v>
+        <v>7047574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562394</v>
+        <v>121562403</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416218</v>
+        <v>416432</v>
       </c>
       <c r="R19" t="n">
-        <v>7047582</v>
+        <v>7047696</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562384</v>
+        <v>121562404</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416263</v>
+        <v>416533</v>
       </c>
       <c r="R20" t="n">
-        <v>7047490</v>
+        <v>7047678</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562406</v>
+        <v>121562392</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416562</v>
+        <v>416156</v>
       </c>
       <c r="R22" t="n">
-        <v>7047700</v>
+        <v>7047605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562382</v>
+        <v>121562381</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416431</v>
+        <v>416464</v>
       </c>
       <c r="R23" t="n">
-        <v>7047412</v>
+        <v>7047388</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562404</v>
+        <v>121562383</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416533</v>
+        <v>416419</v>
       </c>
       <c r="R24" t="n">
-        <v>7047678</v>
+        <v>7047402</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562398</v>
+        <v>121562406</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416421</v>
+        <v>416562</v>
       </c>
       <c r="R25" t="n">
-        <v>7047618</v>
+        <v>7047700</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562390</v>
+        <v>121562384</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416139</v>
+        <v>416263</v>
       </c>
       <c r="R26" t="n">
-        <v>7047589</v>
+        <v>7047490</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562396</v>
+        <v>121562385</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416304</v>
+        <v>416229</v>
       </c>
       <c r="R27" t="n">
-        <v>7047548</v>
+        <v>7047508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562381</v>
+        <v>121562380</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416464</v>
+        <v>416570</v>
       </c>
       <c r="R28" t="n">
-        <v>7047388</v>
+        <v>7047580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562388</v>
+        <v>121562389</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416185</v>
+        <v>416120</v>
       </c>
       <c r="R29" t="n">
-        <v>7047533</v>
+        <v>7047580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562389</v>
+        <v>121562407</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416120</v>
+        <v>416664</v>
       </c>
       <c r="R30" t="n">
-        <v>7047580</v>
+        <v>7047789</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562394</v>
+        <v>121562386</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416218</v>
+        <v>416228</v>
       </c>
       <c r="R5" t="n">
-        <v>7047582</v>
+        <v>7047510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562386</v>
+        <v>121562394</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416228</v>
+        <v>416218</v>
       </c>
       <c r="R6" t="n">
-        <v>7047510</v>
+        <v>7047582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562397</v>
+        <v>121562387</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416318</v>
+        <v>416169</v>
       </c>
       <c r="R3" t="n">
-        <v>7047519</v>
+        <v>7047551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562396</v>
+        <v>121562402</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416304</v>
+        <v>416433</v>
       </c>
       <c r="R4" t="n">
-        <v>7047548</v>
+        <v>7047695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562386</v>
+        <v>121562401</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416228</v>
+        <v>416440</v>
       </c>
       <c r="R5" t="n">
-        <v>7047510</v>
+        <v>7047666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562394</v>
+        <v>121562397</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416218</v>
+        <v>416318</v>
       </c>
       <c r="R6" t="n">
-        <v>7047582</v>
+        <v>7047519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562387</v>
+        <v>121562407</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416169</v>
+        <v>416664</v>
       </c>
       <c r="R7" t="n">
-        <v>7047551</v>
+        <v>7047789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562388</v>
+        <v>121562400</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416185</v>
+        <v>416426</v>
       </c>
       <c r="R8" t="n">
-        <v>7047533</v>
+        <v>7047612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562402</v>
+        <v>121562381</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416433</v>
+        <v>416464</v>
       </c>
       <c r="R9" t="n">
-        <v>7047695</v>
+        <v>7047388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562391</v>
+        <v>121562388</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416161</v>
+        <v>416185</v>
       </c>
       <c r="R10" t="n">
-        <v>7047590</v>
+        <v>7047533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562401</v>
+        <v>121562389</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416440</v>
+        <v>416120</v>
       </c>
       <c r="R11" t="n">
-        <v>7047666</v>
+        <v>7047580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562382</v>
+        <v>121562394</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416431</v>
+        <v>416218</v>
       </c>
       <c r="R12" t="n">
-        <v>7047412</v>
+        <v>7047582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562398</v>
+        <v>121562384</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416421</v>
+        <v>416263</v>
       </c>
       <c r="R13" t="n">
-        <v>7047618</v>
+        <v>7047490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562405</v>
+        <v>121562379</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416545</v>
+        <v>416590</v>
       </c>
       <c r="R14" t="n">
-        <v>7047634</v>
+        <v>7047648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562390</v>
+        <v>121562385</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416139</v>
+        <v>416229</v>
       </c>
       <c r="R15" t="n">
-        <v>7047589</v>
+        <v>7047508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562379</v>
+        <v>121562403</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416590</v>
+        <v>416432</v>
       </c>
       <c r="R16" t="n">
-        <v>7047648</v>
+        <v>7047696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562393</v>
+        <v>121562392</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416175</v>
+        <v>416156</v>
       </c>
       <c r="R17" t="n">
-        <v>7047616</v>
+        <v>7047605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562395</v>
+        <v>121562405</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416317</v>
+        <v>416545</v>
       </c>
       <c r="R18" t="n">
-        <v>7047574</v>
+        <v>7047634</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562403</v>
+        <v>121562390</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416432</v>
+        <v>416139</v>
       </c>
       <c r="R19" t="n">
-        <v>7047696</v>
+        <v>7047589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562404</v>
+        <v>121562393</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416533</v>
+        <v>416175</v>
       </c>
       <c r="R20" t="n">
-        <v>7047678</v>
+        <v>7047616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562400</v>
+        <v>121562391</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416426</v>
+        <v>416161</v>
       </c>
       <c r="R21" t="n">
-        <v>7047612</v>
+        <v>7047590</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562392</v>
+        <v>121562380</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416156</v>
+        <v>416570</v>
       </c>
       <c r="R22" t="n">
-        <v>7047605</v>
+        <v>7047580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562381</v>
+        <v>121562386</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416464</v>
+        <v>416228</v>
       </c>
       <c r="R23" t="n">
-        <v>7047388</v>
+        <v>7047510</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562383</v>
+        <v>121562406</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416419</v>
+        <v>416562</v>
       </c>
       <c r="R24" t="n">
-        <v>7047402</v>
+        <v>7047700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562406</v>
+        <v>121562396</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416562</v>
+        <v>416304</v>
       </c>
       <c r="R25" t="n">
-        <v>7047700</v>
+        <v>7047548</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562384</v>
+        <v>121562382</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416263</v>
+        <v>416431</v>
       </c>
       <c r="R26" t="n">
-        <v>7047490</v>
+        <v>7047412</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562385</v>
+        <v>121562404</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416229</v>
+        <v>416533</v>
       </c>
       <c r="R27" t="n">
-        <v>7047508</v>
+        <v>7047678</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562380</v>
+        <v>121562398</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416570</v>
+        <v>416421</v>
       </c>
       <c r="R28" t="n">
-        <v>7047580</v>
+        <v>7047618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562389</v>
+        <v>121562383</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416120</v>
+        <v>416419</v>
       </c>
       <c r="R29" t="n">
-        <v>7047580</v>
+        <v>7047402</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562407</v>
+        <v>121562395</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416664</v>
+        <v>416317</v>
       </c>
       <c r="R30" t="n">
-        <v>7047789</v>
+        <v>7047574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562389</v>
+        <v>121562406</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416120</v>
+        <v>416562</v>
       </c>
       <c r="R3" t="n">
-        <v>7047580</v>
+        <v>7047700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562382</v>
+        <v>121562384</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416431</v>
+        <v>416263</v>
       </c>
       <c r="R4" t="n">
-        <v>7047412</v>
+        <v>7047490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562385</v>
+        <v>121562402</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416229</v>
+        <v>416433</v>
       </c>
       <c r="R5" t="n">
-        <v>7047508</v>
+        <v>7047695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562405</v>
+        <v>121562383</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416545</v>
+        <v>416419</v>
       </c>
       <c r="R6" t="n">
-        <v>7047634</v>
+        <v>7047402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562379</v>
+        <v>121562401</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416590</v>
+        <v>416440</v>
       </c>
       <c r="R7" t="n">
-        <v>7047648</v>
+        <v>7047666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562394</v>
+        <v>121562404</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416218</v>
+        <v>416533</v>
       </c>
       <c r="R8" t="n">
-        <v>7047582</v>
+        <v>7047678</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562387</v>
+        <v>121562381</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416169</v>
+        <v>416464</v>
       </c>
       <c r="R9" t="n">
-        <v>7047551</v>
+        <v>7047388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562393</v>
+        <v>121562392</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416175</v>
+        <v>416156</v>
       </c>
       <c r="R10" t="n">
-        <v>7047616</v>
+        <v>7047605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562400</v>
+        <v>121562382</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416426</v>
+        <v>416431</v>
       </c>
       <c r="R11" t="n">
-        <v>7047612</v>
+        <v>7047412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562406</v>
+        <v>121562398</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416562</v>
+        <v>416421</v>
       </c>
       <c r="R12" t="n">
-        <v>7047700</v>
+        <v>7047618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562388</v>
+        <v>121562386</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416185</v>
+        <v>416228</v>
       </c>
       <c r="R13" t="n">
-        <v>7047533</v>
+        <v>7047510</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562386</v>
+        <v>121562407</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416228</v>
+        <v>416664</v>
       </c>
       <c r="R14" t="n">
-        <v>7047510</v>
+        <v>7047789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562390</v>
+        <v>121562380</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416139</v>
+        <v>416570</v>
       </c>
       <c r="R15" t="n">
-        <v>7047589</v>
+        <v>7047580</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562391</v>
+        <v>121562387</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416161</v>
+        <v>416169</v>
       </c>
       <c r="R16" t="n">
-        <v>7047590</v>
+        <v>7047551</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562407</v>
+        <v>121562395</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416664</v>
+        <v>416317</v>
       </c>
       <c r="R17" t="n">
-        <v>7047789</v>
+        <v>7047574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562398</v>
+        <v>121562403</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416421</v>
+        <v>416432</v>
       </c>
       <c r="R18" t="n">
-        <v>7047618</v>
+        <v>7047696</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562401</v>
+        <v>121562389</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416440</v>
+        <v>416120</v>
       </c>
       <c r="R19" t="n">
-        <v>7047666</v>
+        <v>7047580</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562397</v>
+        <v>121562394</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416318</v>
+        <v>416218</v>
       </c>
       <c r="R20" t="n">
-        <v>7047519</v>
+        <v>7047582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562403</v>
+        <v>121562379</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416432</v>
+        <v>416590</v>
       </c>
       <c r="R21" t="n">
-        <v>7047696</v>
+        <v>7047648</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562383</v>
+        <v>121562388</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416419</v>
+        <v>416185</v>
       </c>
       <c r="R22" t="n">
-        <v>7047402</v>
+        <v>7047533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562381</v>
+        <v>121562405</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416464</v>
+        <v>416545</v>
       </c>
       <c r="R23" t="n">
-        <v>7047388</v>
+        <v>7047634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562404</v>
+        <v>121562400</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416533</v>
+        <v>416426</v>
       </c>
       <c r="R24" t="n">
-        <v>7047678</v>
+        <v>7047612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562395</v>
+        <v>121562390</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416317</v>
+        <v>416139</v>
       </c>
       <c r="R25" t="n">
-        <v>7047574</v>
+        <v>7047589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562402</v>
+        <v>121562385</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416433</v>
+        <v>416229</v>
       </c>
       <c r="R26" t="n">
-        <v>7047695</v>
+        <v>7047508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562380</v>
+        <v>121562396</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416570</v>
+        <v>416304</v>
       </c>
       <c r="R27" t="n">
-        <v>7047580</v>
+        <v>7047548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562392</v>
+        <v>121562397</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416156</v>
+        <v>416318</v>
       </c>
       <c r="R28" t="n">
-        <v>7047605</v>
+        <v>7047519</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562384</v>
+        <v>121562391</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416263</v>
+        <v>416161</v>
       </c>
       <c r="R29" t="n">
-        <v>7047490</v>
+        <v>7047590</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562396</v>
+        <v>121562393</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416304</v>
+        <v>416175</v>
       </c>
       <c r="R30" t="n">
-        <v>7047548</v>
+        <v>7047616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562406</v>
+        <v>121562403</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416562</v>
+        <v>416432</v>
       </c>
       <c r="R3" t="n">
-        <v>7047700</v>
+        <v>7047696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562384</v>
+        <v>121562396</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416263</v>
+        <v>416304</v>
       </c>
       <c r="R4" t="n">
-        <v>7047490</v>
+        <v>7047548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562402</v>
+        <v>121562398</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416433</v>
+        <v>416421</v>
       </c>
       <c r="R5" t="n">
-        <v>7047695</v>
+        <v>7047618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562383</v>
+        <v>121562384</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416419</v>
+        <v>416263</v>
       </c>
       <c r="R6" t="n">
-        <v>7047402</v>
+        <v>7047490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562401</v>
+        <v>121562386</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416440</v>
+        <v>416228</v>
       </c>
       <c r="R7" t="n">
-        <v>7047666</v>
+        <v>7047510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562404</v>
+        <v>121562383</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416533</v>
+        <v>416419</v>
       </c>
       <c r="R8" t="n">
-        <v>7047678</v>
+        <v>7047402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562381</v>
+        <v>121562389</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416464</v>
+        <v>416120</v>
       </c>
       <c r="R9" t="n">
-        <v>7047388</v>
+        <v>7047580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562392</v>
+        <v>121562387</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416156</v>
+        <v>416169</v>
       </c>
       <c r="R10" t="n">
-        <v>7047605</v>
+        <v>7047551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562382</v>
+        <v>121562405</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416431</v>
+        <v>416545</v>
       </c>
       <c r="R11" t="n">
-        <v>7047412</v>
+        <v>7047634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562398</v>
+        <v>121562401</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416421</v>
+        <v>416440</v>
       </c>
       <c r="R12" t="n">
-        <v>7047618</v>
+        <v>7047666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562386</v>
+        <v>121562379</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416228</v>
+        <v>416590</v>
       </c>
       <c r="R13" t="n">
-        <v>7047510</v>
+        <v>7047648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562407</v>
+        <v>121562406</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416664</v>
+        <v>416562</v>
       </c>
       <c r="R14" t="n">
-        <v>7047789</v>
+        <v>7047700</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562380</v>
+        <v>121562382</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416570</v>
+        <v>416431</v>
       </c>
       <c r="R15" t="n">
-        <v>7047580</v>
+        <v>7047412</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562387</v>
+        <v>121562395</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416169</v>
+        <v>416317</v>
       </c>
       <c r="R16" t="n">
-        <v>7047551</v>
+        <v>7047574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562395</v>
+        <v>121562400</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416317</v>
+        <v>416426</v>
       </c>
       <c r="R17" t="n">
-        <v>7047574</v>
+        <v>7047612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562403</v>
+        <v>121562397</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416432</v>
+        <v>416318</v>
       </c>
       <c r="R18" t="n">
-        <v>7047696</v>
+        <v>7047519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562389</v>
+        <v>121562404</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416120</v>
+        <v>416533</v>
       </c>
       <c r="R19" t="n">
-        <v>7047580</v>
+        <v>7047678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562394</v>
+        <v>121562390</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416218</v>
+        <v>416139</v>
       </c>
       <c r="R20" t="n">
-        <v>7047582</v>
+        <v>7047589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562379</v>
+        <v>121562392</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416590</v>
+        <v>416156</v>
       </c>
       <c r="R21" t="n">
-        <v>7047648</v>
+        <v>7047605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562388</v>
+        <v>121562402</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416185</v>
+        <v>416433</v>
       </c>
       <c r="R22" t="n">
-        <v>7047533</v>
+        <v>7047695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562405</v>
+        <v>121562407</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416545</v>
+        <v>416664</v>
       </c>
       <c r="R23" t="n">
-        <v>7047634</v>
+        <v>7047789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562400</v>
+        <v>121562393</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416426</v>
+        <v>416175</v>
       </c>
       <c r="R24" t="n">
-        <v>7047612</v>
+        <v>7047616</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562390</v>
+        <v>121562394</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416139</v>
+        <v>416218</v>
       </c>
       <c r="R25" t="n">
-        <v>7047589</v>
+        <v>7047582</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562385</v>
+        <v>121562391</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416229</v>
+        <v>416161</v>
       </c>
       <c r="R26" t="n">
-        <v>7047508</v>
+        <v>7047590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562396</v>
+        <v>121562380</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416304</v>
+        <v>416570</v>
       </c>
       <c r="R27" t="n">
-        <v>7047548</v>
+        <v>7047580</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562397</v>
+        <v>121562381</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416318</v>
+        <v>416464</v>
       </c>
       <c r="R28" t="n">
-        <v>7047519</v>
+        <v>7047388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562391</v>
+        <v>121562388</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416161</v>
+        <v>416185</v>
       </c>
       <c r="R29" t="n">
-        <v>7047590</v>
+        <v>7047533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562393</v>
+        <v>121562385</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416175</v>
+        <v>416229</v>
       </c>
       <c r="R30" t="n">
-        <v>7047616</v>
+        <v>7047508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562403</v>
+        <v>121562407</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416432</v>
+        <v>416664</v>
       </c>
       <c r="R3" t="n">
-        <v>7047696</v>
+        <v>7047789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562396</v>
+        <v>121562380</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416304</v>
+        <v>416570</v>
       </c>
       <c r="R4" t="n">
-        <v>7047548</v>
+        <v>7047580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562398</v>
+        <v>121562382</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416421</v>
+        <v>416431</v>
       </c>
       <c r="R5" t="n">
-        <v>7047618</v>
+        <v>7047412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562384</v>
+        <v>121562404</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416263</v>
+        <v>416533</v>
       </c>
       <c r="R6" t="n">
-        <v>7047490</v>
+        <v>7047678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562386</v>
+        <v>121562400</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416228</v>
+        <v>416426</v>
       </c>
       <c r="R7" t="n">
-        <v>7047510</v>
+        <v>7047612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562383</v>
+        <v>121562387</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416419</v>
+        <v>416169</v>
       </c>
       <c r="R8" t="n">
-        <v>7047402</v>
+        <v>7047551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562389</v>
+        <v>121562392</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416120</v>
+        <v>416156</v>
       </c>
       <c r="R9" t="n">
-        <v>7047580</v>
+        <v>7047605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562387</v>
+        <v>121562396</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416169</v>
+        <v>416304</v>
       </c>
       <c r="R10" t="n">
-        <v>7047551</v>
+        <v>7047548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562405</v>
+        <v>121562403</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416545</v>
+        <v>416432</v>
       </c>
       <c r="R11" t="n">
-        <v>7047634</v>
+        <v>7047696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562401</v>
+        <v>121562402</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416440</v>
+        <v>416433</v>
       </c>
       <c r="R12" t="n">
-        <v>7047666</v>
+        <v>7047695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562379</v>
+        <v>121562384</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416590</v>
+        <v>416263</v>
       </c>
       <c r="R13" t="n">
-        <v>7047648</v>
+        <v>7047490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562406</v>
+        <v>121562385</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416562</v>
+        <v>416229</v>
       </c>
       <c r="R14" t="n">
-        <v>7047700</v>
+        <v>7047508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562382</v>
+        <v>121562397</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416431</v>
+        <v>416318</v>
       </c>
       <c r="R15" t="n">
-        <v>7047412</v>
+        <v>7047519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562395</v>
+        <v>121562389</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416317</v>
+        <v>416120</v>
       </c>
       <c r="R16" t="n">
-        <v>7047574</v>
+        <v>7047580</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562400</v>
+        <v>121562381</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416426</v>
+        <v>416464</v>
       </c>
       <c r="R17" t="n">
-        <v>7047612</v>
+        <v>7047388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562397</v>
+        <v>121562398</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416318</v>
+        <v>416421</v>
       </c>
       <c r="R18" t="n">
-        <v>7047519</v>
+        <v>7047618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562404</v>
+        <v>121562394</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416533</v>
+        <v>416218</v>
       </c>
       <c r="R19" t="n">
-        <v>7047678</v>
+        <v>7047582</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562392</v>
+        <v>121562401</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416156</v>
+        <v>416440</v>
       </c>
       <c r="R21" t="n">
-        <v>7047605</v>
+        <v>7047666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562402</v>
+        <v>121562406</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416433</v>
+        <v>416562</v>
       </c>
       <c r="R22" t="n">
-        <v>7047695</v>
+        <v>7047700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562407</v>
+        <v>121562393</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416664</v>
+        <v>416175</v>
       </c>
       <c r="R23" t="n">
-        <v>7047789</v>
+        <v>7047616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562393</v>
+        <v>121562395</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416175</v>
+        <v>416317</v>
       </c>
       <c r="R24" t="n">
-        <v>7047616</v>
+        <v>7047574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562394</v>
+        <v>121562388</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416218</v>
+        <v>416185</v>
       </c>
       <c r="R25" t="n">
-        <v>7047582</v>
+        <v>7047533</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562391</v>
+        <v>121562405</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416161</v>
+        <v>416545</v>
       </c>
       <c r="R26" t="n">
-        <v>7047590</v>
+        <v>7047634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562380</v>
+        <v>121562386</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416570</v>
+        <v>416228</v>
       </c>
       <c r="R27" t="n">
-        <v>7047580</v>
+        <v>7047510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562381</v>
+        <v>121562383</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416464</v>
+        <v>416419</v>
       </c>
       <c r="R28" t="n">
-        <v>7047388</v>
+        <v>7047402</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562388</v>
+        <v>121562379</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416185</v>
+        <v>416590</v>
       </c>
       <c r="R29" t="n">
-        <v>7047533</v>
+        <v>7047648</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562385</v>
+        <v>121562391</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416229</v>
+        <v>416161</v>
       </c>
       <c r="R30" t="n">
-        <v>7047508</v>
+        <v>7047590</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562407</v>
+        <v>121562392</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416664</v>
+        <v>416156</v>
       </c>
       <c r="R3" t="n">
-        <v>7047789</v>
+        <v>7047605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562380</v>
+        <v>121562390</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416570</v>
+        <v>416139</v>
       </c>
       <c r="R4" t="n">
-        <v>7047580</v>
+        <v>7047589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562382</v>
+        <v>121562402</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416431</v>
+        <v>416433</v>
       </c>
       <c r="R5" t="n">
-        <v>7047412</v>
+        <v>7047695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562404</v>
+        <v>121562388</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416533</v>
+        <v>416185</v>
       </c>
       <c r="R6" t="n">
-        <v>7047678</v>
+        <v>7047533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562400</v>
+        <v>121562393</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416426</v>
+        <v>416175</v>
       </c>
       <c r="R7" t="n">
-        <v>7047612</v>
+        <v>7047616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562387</v>
+        <v>121562382</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416169</v>
+        <v>416431</v>
       </c>
       <c r="R8" t="n">
-        <v>7047551</v>
+        <v>7047412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562392</v>
+        <v>121562379</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416156</v>
+        <v>416590</v>
       </c>
       <c r="R9" t="n">
-        <v>7047605</v>
+        <v>7047648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562396</v>
+        <v>121562400</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416304</v>
+        <v>416426</v>
       </c>
       <c r="R10" t="n">
-        <v>7047548</v>
+        <v>7047612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562403</v>
+        <v>121562386</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416432</v>
+        <v>416228</v>
       </c>
       <c r="R11" t="n">
-        <v>7047696</v>
+        <v>7047510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562402</v>
+        <v>121562389</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416433</v>
+        <v>416120</v>
       </c>
       <c r="R12" t="n">
-        <v>7047695</v>
+        <v>7047580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562385</v>
+        <v>121562395</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416229</v>
+        <v>416317</v>
       </c>
       <c r="R14" t="n">
-        <v>7047508</v>
+        <v>7047574</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562389</v>
+        <v>121562394</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416120</v>
+        <v>416218</v>
       </c>
       <c r="R16" t="n">
-        <v>7047580</v>
+        <v>7047582</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562381</v>
+        <v>121562398</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416464</v>
+        <v>416421</v>
       </c>
       <c r="R17" t="n">
-        <v>7047388</v>
+        <v>7047618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562398</v>
+        <v>121562383</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416421</v>
+        <v>416419</v>
       </c>
       <c r="R18" t="n">
-        <v>7047618</v>
+        <v>7047402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562394</v>
+        <v>121562404</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416218</v>
+        <v>416533</v>
       </c>
       <c r="R19" t="n">
-        <v>7047582</v>
+        <v>7047678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562390</v>
+        <v>121562407</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416139</v>
+        <v>416664</v>
       </c>
       <c r="R20" t="n">
-        <v>7047589</v>
+        <v>7047789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562401</v>
+        <v>121562403</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416440</v>
+        <v>416432</v>
       </c>
       <c r="R21" t="n">
-        <v>7047666</v>
+        <v>7047696</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562406</v>
+        <v>121562380</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416562</v>
+        <v>416570</v>
       </c>
       <c r="R22" t="n">
-        <v>7047700</v>
+        <v>7047580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562393</v>
+        <v>121562405</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416175</v>
+        <v>416545</v>
       </c>
       <c r="R23" t="n">
-        <v>7047616</v>
+        <v>7047634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562395</v>
+        <v>121562387</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416317</v>
+        <v>416169</v>
       </c>
       <c r="R24" t="n">
-        <v>7047574</v>
+        <v>7047551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562388</v>
+        <v>121562401</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416185</v>
+        <v>416440</v>
       </c>
       <c r="R25" t="n">
-        <v>7047533</v>
+        <v>7047666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562405</v>
+        <v>121562396</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416545</v>
+        <v>416304</v>
       </c>
       <c r="R26" t="n">
-        <v>7047634</v>
+        <v>7047548</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562386</v>
+        <v>121562406</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416228</v>
+        <v>416562</v>
       </c>
       <c r="R27" t="n">
-        <v>7047510</v>
+        <v>7047700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562383</v>
+        <v>121562391</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416419</v>
+        <v>416161</v>
       </c>
       <c r="R28" t="n">
-        <v>7047402</v>
+        <v>7047590</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562379</v>
+        <v>121562385</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416590</v>
+        <v>416229</v>
       </c>
       <c r="R29" t="n">
-        <v>7047648</v>
+        <v>7047508</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562391</v>
+        <v>121562381</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416161</v>
+        <v>416464</v>
       </c>
       <c r="R30" t="n">
-        <v>7047590</v>
+        <v>7047388</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562392</v>
+        <v>121562403</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416156</v>
+        <v>416432</v>
       </c>
       <c r="R3" t="n">
-        <v>7047605</v>
+        <v>7047696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562390</v>
+        <v>121562396</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416139</v>
+        <v>416304</v>
       </c>
       <c r="R4" t="n">
-        <v>7047589</v>
+        <v>7047548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562402</v>
+        <v>121562379</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416433</v>
+        <v>416590</v>
       </c>
       <c r="R5" t="n">
-        <v>7047695</v>
+        <v>7047648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562388</v>
+        <v>121562382</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416185</v>
+        <v>416431</v>
       </c>
       <c r="R6" t="n">
-        <v>7047533</v>
+        <v>7047412</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562393</v>
+        <v>121562405</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416175</v>
+        <v>416545</v>
       </c>
       <c r="R7" t="n">
-        <v>7047616</v>
+        <v>7047634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562382</v>
+        <v>121562406</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416431</v>
+        <v>416562</v>
       </c>
       <c r="R8" t="n">
-        <v>7047412</v>
+        <v>7047700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562379</v>
+        <v>121562384</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416590</v>
+        <v>416263</v>
       </c>
       <c r="R9" t="n">
-        <v>7047648</v>
+        <v>7047490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562400</v>
+        <v>121562380</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416426</v>
+        <v>416570</v>
       </c>
       <c r="R10" t="n">
-        <v>7047612</v>
+        <v>7047580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562386</v>
+        <v>121562401</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416228</v>
+        <v>416440</v>
       </c>
       <c r="R11" t="n">
-        <v>7047510</v>
+        <v>7047666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562389</v>
+        <v>121562388</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416120</v>
+        <v>416185</v>
       </c>
       <c r="R12" t="n">
-        <v>7047580</v>
+        <v>7047533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562384</v>
+        <v>121562400</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416263</v>
+        <v>416426</v>
       </c>
       <c r="R13" t="n">
-        <v>7047490</v>
+        <v>7047612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562395</v>
+        <v>121562386</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416317</v>
+        <v>416228</v>
       </c>
       <c r="R14" t="n">
-        <v>7047574</v>
+        <v>7047510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562397</v>
+        <v>121562390</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416318</v>
+        <v>416139</v>
       </c>
       <c r="R15" t="n">
-        <v>7047519</v>
+        <v>7047589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562394</v>
+        <v>121562398</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416218</v>
+        <v>416421</v>
       </c>
       <c r="R16" t="n">
-        <v>7047582</v>
+        <v>7047618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562398</v>
+        <v>121562397</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416421</v>
+        <v>416318</v>
       </c>
       <c r="R17" t="n">
-        <v>7047618</v>
+        <v>7047519</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562383</v>
+        <v>121562395</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416419</v>
+        <v>416317</v>
       </c>
       <c r="R18" t="n">
-        <v>7047402</v>
+        <v>7047574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562404</v>
+        <v>121562391</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416533</v>
+        <v>416161</v>
       </c>
       <c r="R19" t="n">
-        <v>7047678</v>
+        <v>7047590</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562407</v>
+        <v>121562392</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416664</v>
+        <v>416156</v>
       </c>
       <c r="R20" t="n">
-        <v>7047789</v>
+        <v>7047605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562403</v>
+        <v>121562383</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416432</v>
+        <v>416419</v>
       </c>
       <c r="R21" t="n">
-        <v>7047696</v>
+        <v>7047402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562380</v>
+        <v>121562404</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416570</v>
+        <v>416533</v>
       </c>
       <c r="R22" t="n">
-        <v>7047580</v>
+        <v>7047678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562405</v>
+        <v>121562387</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416545</v>
+        <v>416169</v>
       </c>
       <c r="R23" t="n">
-        <v>7047634</v>
+        <v>7047551</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562387</v>
+        <v>121562407</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416169</v>
+        <v>416664</v>
       </c>
       <c r="R24" t="n">
-        <v>7047551</v>
+        <v>7047789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562401</v>
+        <v>121562381</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416440</v>
+        <v>416464</v>
       </c>
       <c r="R25" t="n">
-        <v>7047666</v>
+        <v>7047388</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562396</v>
+        <v>121562402</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416304</v>
+        <v>416433</v>
       </c>
       <c r="R26" t="n">
-        <v>7047548</v>
+        <v>7047695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562406</v>
+        <v>121562394</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416562</v>
+        <v>416218</v>
       </c>
       <c r="R27" t="n">
-        <v>7047700</v>
+        <v>7047582</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562391</v>
+        <v>121562389</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416161</v>
+        <v>416120</v>
       </c>
       <c r="R28" t="n">
-        <v>7047590</v>
+        <v>7047580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562385</v>
+        <v>121562393</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416229</v>
+        <v>416175</v>
       </c>
       <c r="R29" t="n">
-        <v>7047508</v>
+        <v>7047616</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562381</v>
+        <v>121562385</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416464</v>
+        <v>416229</v>
       </c>
       <c r="R30" t="n">
-        <v>7047388</v>
+        <v>7047508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562403</v>
+        <v>121562387</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416432</v>
+        <v>416169</v>
       </c>
       <c r="R3" t="n">
-        <v>7047696</v>
+        <v>7047551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562396</v>
+        <v>121562405</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416304</v>
+        <v>416545</v>
       </c>
       <c r="R4" t="n">
-        <v>7047548</v>
+        <v>7047634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562379</v>
+        <v>121562397</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416590</v>
+        <v>416318</v>
       </c>
       <c r="R5" t="n">
-        <v>7047648</v>
+        <v>7047519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562382</v>
+        <v>121562401</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416431</v>
+        <v>416440</v>
       </c>
       <c r="R6" t="n">
-        <v>7047412</v>
+        <v>7047666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562405</v>
+        <v>121562393</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416545</v>
+        <v>416175</v>
       </c>
       <c r="R7" t="n">
-        <v>7047634</v>
+        <v>7047616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562406</v>
+        <v>121562392</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416562</v>
+        <v>416156</v>
       </c>
       <c r="R8" t="n">
-        <v>7047700</v>
+        <v>7047605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562384</v>
+        <v>121562382</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416263</v>
+        <v>416431</v>
       </c>
       <c r="R9" t="n">
-        <v>7047490</v>
+        <v>7047412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562380</v>
+        <v>121562398</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416570</v>
+        <v>416421</v>
       </c>
       <c r="R10" t="n">
-        <v>7047580</v>
+        <v>7047618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562401</v>
+        <v>121562407</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416440</v>
+        <v>416664</v>
       </c>
       <c r="R11" t="n">
-        <v>7047666</v>
+        <v>7047789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562388</v>
+        <v>121562406</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416185</v>
+        <v>416562</v>
       </c>
       <c r="R12" t="n">
-        <v>7047533</v>
+        <v>7047700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562400</v>
+        <v>121562403</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416426</v>
+        <v>416432</v>
       </c>
       <c r="R13" t="n">
-        <v>7047612</v>
+        <v>7047696</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562386</v>
+        <v>121562385</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416228</v>
+        <v>416229</v>
       </c>
       <c r="R14" t="n">
-        <v>7047510</v>
+        <v>7047508</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562390</v>
+        <v>121562394</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416139</v>
+        <v>416218</v>
       </c>
       <c r="R15" t="n">
-        <v>7047589</v>
+        <v>7047582</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562398</v>
+        <v>121562395</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416421</v>
+        <v>416317</v>
       </c>
       <c r="R16" t="n">
-        <v>7047618</v>
+        <v>7047574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562397</v>
+        <v>121562388</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416318</v>
+        <v>416185</v>
       </c>
       <c r="R17" t="n">
-        <v>7047519</v>
+        <v>7047533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562395</v>
+        <v>121562381</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416317</v>
+        <v>416464</v>
       </c>
       <c r="R18" t="n">
-        <v>7047574</v>
+        <v>7047388</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562391</v>
+        <v>121562386</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416161</v>
+        <v>416228</v>
       </c>
       <c r="R19" t="n">
-        <v>7047590</v>
+        <v>7047510</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562392</v>
+        <v>121562400</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416156</v>
+        <v>416426</v>
       </c>
       <c r="R20" t="n">
-        <v>7047605</v>
+        <v>7047612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,7 +2829,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562404</v>
+        <v>121562396</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416533</v>
+        <v>416304</v>
       </c>
       <c r="R22" t="n">
-        <v>7047678</v>
+        <v>7047548</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562387</v>
+        <v>121562402</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416169</v>
+        <v>416433</v>
       </c>
       <c r="R23" t="n">
-        <v>7047551</v>
+        <v>7047695</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562407</v>
+        <v>121562389</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416664</v>
+        <v>416120</v>
       </c>
       <c r="R24" t="n">
-        <v>7047789</v>
+        <v>7047580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562381</v>
+        <v>121562384</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416464</v>
+        <v>416263</v>
       </c>
       <c r="R25" t="n">
-        <v>7047388</v>
+        <v>7047490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562402</v>
+        <v>121562379</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>416433</v>
+        <v>416590</v>
       </c>
       <c r="R26" t="n">
-        <v>7047695</v>
+        <v>7047648</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562394</v>
+        <v>121562390</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416218</v>
+        <v>416139</v>
       </c>
       <c r="R27" t="n">
-        <v>7047582</v>
+        <v>7047589</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562389</v>
+        <v>121562391</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416120</v>
+        <v>416161</v>
       </c>
       <c r="R28" t="n">
-        <v>7047580</v>
+        <v>7047590</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562393</v>
+        <v>121562380</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416175</v>
+        <v>416570</v>
       </c>
       <c r="R29" t="n">
-        <v>7047616</v>
+        <v>7047580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562385</v>
+        <v>121562404</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416229</v>
+        <v>416533</v>
       </c>
       <c r="R30" t="n">
-        <v>7047508</v>
+        <v>7047678</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,6 +3790,3099 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127660844</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>416391</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7047429</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127661196</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75125</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127661193</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80081</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127661200</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127661184</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>416548</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7047658</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På grangren! Ej under asp! Gran ca 30 cm i diameter i gammal granskog, en död björk finns som kan ha fungerat som krondroppsträd</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127660840</v>
+      </c>
+      <c r="B36" t="n">
+        <v>105469</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7047463</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127660829</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127661195</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80156</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127660831</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>416545</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7047606</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127660843</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7047463</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127661199</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127661203</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79177</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>416376</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7047411</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gren på gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127661202</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>416376</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7047411</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127661194</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80157</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127661192</v>
+      </c>
+      <c r="B45" t="n">
+        <v>75137</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>310</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127660842</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7047463</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127661197</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79274</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127660828</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127660826</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i gammal gles ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127660834</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7047565</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127661185</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79099</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>283</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>416559</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7047617</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127660830</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75008</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127660833</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80081</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7047565</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127660825</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>416539</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7047696</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 lockande</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127660827</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På marken i gammal gles ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127661187</v>
+      </c>
+      <c r="B56" t="n">
+        <v>103893</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7047573</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127660832</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80122</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7047565</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127661185</v>
+        <v>127660830</v>
       </c>
       <c r="B51" t="n">
-        <v>79099</v>
+        <v>75008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>283</v>
+        <v>229654</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416559</v>
+        <v>416550</v>
       </c>
       <c r="R51" t="n">
-        <v>7047617</v>
+        <v>7047647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,60 +6191,60 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127660830</v>
+        <v>127661185</v>
       </c>
       <c r="B52" t="n">
-        <v>75008</v>
+        <v>79099</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229654</v>
+        <v>283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416550</v>
+        <v>416559</v>
       </c>
       <c r="R52" t="n">
-        <v>7047647</v>
+        <v>7047617</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,28 +6308,28 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>80122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R31" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,60 +3881,60 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661196</v>
+        <v>127660844</v>
       </c>
       <c r="B32" t="n">
-        <v>75125</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R32" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,38 +3998,38 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661193</v>
+        <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>80081</v>
+        <v>75125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4143,32 +4143,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661200</v>
+        <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>80122</v>
+        <v>80081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80122</v>
+        <v>80156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R37" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80156</v>
+        <v>80122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R38" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661203</v>
+        <v>127661202</v>
       </c>
       <c r="B42" t="n">
-        <v>79177</v>
+        <v>80122</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661202</v>
+        <v>127661203</v>
       </c>
       <c r="B43" t="n">
-        <v>80122</v>
+        <v>79177</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B45" t="n">
-        <v>75137</v>
+        <v>80122</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R45" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B46" t="n">
-        <v>80122</v>
+        <v>75137</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R46" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>80121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R49" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,6 +5969,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5985,32 +6000,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>80121</v>
+        <v>98781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6020,10 +6035,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R50" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6071,21 +6086,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127660830</v>
+        <v>127661185</v>
       </c>
       <c r="B51" t="n">
-        <v>75008</v>
+        <v>79099</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229654</v>
+        <v>283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416550</v>
+        <v>416559</v>
       </c>
       <c r="R51" t="n">
-        <v>7047647</v>
+        <v>7047617</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,60 +6191,60 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127661185</v>
+        <v>127660830</v>
       </c>
       <c r="B52" t="n">
-        <v>79099</v>
+        <v>75008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>283</v>
+        <v>229654</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416559</v>
+        <v>416550</v>
       </c>
       <c r="R52" t="n">
-        <v>7047617</v>
+        <v>7047647</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,73 +6308,82 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>80081</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R53" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6411,7 +6420,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,21 +6431,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6453,54 +6447,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B54" t="n">
-        <v>57661</v>
+        <v>80081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R54" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6537,7 +6522,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6548,6 +6533,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6567,7 +6567,7 @@
         <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>80122</v>
+        <v>75137</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R45" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>75137</v>
+        <v>80122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R46" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661200</v>
+        <v>127660844</v>
       </c>
       <c r="B31" t="n">
-        <v>80122</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R31" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,60 +3881,60 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127660844</v>
+        <v>127661196</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>75127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R32" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661196</v>
+        <v>127661200</v>
       </c>
       <c r="B33" t="n">
-        <v>75125</v>
+        <v>80124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,7 +4146,7 @@
         <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>127661184</v>
       </c>
       <c r="B35" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>127660831</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>127660843</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>127661199</v>
       </c>
       <c r="B41" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661202</v>
+        <v>127661203</v>
       </c>
       <c r="B42" t="n">
-        <v>80122</v>
+        <v>79179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661203</v>
+        <v>127661194</v>
       </c>
       <c r="B43" t="n">
-        <v>79177</v>
+        <v>80159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R43" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661194</v>
+        <v>127661202</v>
       </c>
       <c r="B44" t="n">
-        <v>80157</v>
+        <v>80124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R44" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5418,7 +5418,7 @@
         <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>75137</v>
+        <v>75139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>127661197</v>
       </c>
       <c r="B47" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127660828</v>
       </c>
       <c r="B48" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>80121</v>
+        <v>98783</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R49" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,21 +5969,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6000,32 +5985,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B50" t="n">
-        <v>98781</v>
+        <v>80123</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6035,10 +6020,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R50" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6075,7 +6060,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6086,6 +6071,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6105,7 +6105,7 @@
         <v>127661185</v>
       </c>
       <c r="B51" t="n">
-        <v>79099</v>
+        <v>79101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>127660830</v>
       </c>
       <c r="B52" t="n">
-        <v>75008</v>
+        <v>75010</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>127660833</v>
       </c>
       <c r="B54" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B55" t="n">
-        <v>98471</v>
+        <v>103895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B56" t="n">
-        <v>103893</v>
+        <v>98473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
         <v>127660832</v>
       </c>
       <c r="B57" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661203</v>
+        <v>127661202</v>
       </c>
       <c r="B42" t="n">
-        <v>79179</v>
+        <v>80124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661194</v>
+        <v>127661203</v>
       </c>
       <c r="B43" t="n">
-        <v>80159</v>
+        <v>79179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R43" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661202</v>
+        <v>127661194</v>
       </c>
       <c r="B44" t="n">
-        <v>80124</v>
+        <v>80159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R44" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B49" t="n">
-        <v>98783</v>
+        <v>80123</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R49" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,6 +5969,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5985,32 +6000,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>80123</v>
+        <v>98783</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6020,10 +6035,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R50" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6071,21 +6086,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>103895</v>
+        <v>98473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>98473</v>
+        <v>103895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B37" t="n">
-        <v>80158</v>
+        <v>80124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R37" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B38" t="n">
-        <v>80124</v>
+        <v>80158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R38" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>80123</v>
+        <v>98783</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R49" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,21 +5969,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6000,32 +5985,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B50" t="n">
-        <v>98783</v>
+        <v>80123</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6035,10 +6020,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R50" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6075,7 +6060,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6086,6 +6071,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R31" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,60 +3881,60 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661196</v>
+        <v>127660844</v>
       </c>
       <c r="B32" t="n">
-        <v>75127</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R32" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661200</v>
+        <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>80124</v>
+        <v>75127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80124</v>
+        <v>80158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R37" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80158</v>
+        <v>80124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R38" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B45" t="n">
-        <v>75139</v>
+        <v>80124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R45" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B46" t="n">
-        <v>80124</v>
+        <v>75139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R46" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B49" t="n">
-        <v>98783</v>
+        <v>80123</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R49" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,6 +5969,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5985,32 +6000,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>80123</v>
+        <v>98783</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6020,10 +6035,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R50" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6071,21 +6086,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,32 +3792,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661200</v>
+        <v>127661193</v>
       </c>
       <c r="B31" t="n">
-        <v>80124</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R32" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661196</v>
+        <v>127660844</v>
       </c>
       <c r="B33" t="n">
-        <v>75127</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R33" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,38 +4115,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661193</v>
+        <v>127661196</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>75127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661202</v>
+        <v>127661194</v>
       </c>
       <c r="B42" t="n">
-        <v>80124</v>
+        <v>80159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R42" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661194</v>
+        <v>127661202</v>
       </c>
       <c r="B44" t="n">
-        <v>80159</v>
+        <v>80124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R44" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>80124</v>
+        <v>75139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R45" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>75139</v>
+        <v>80124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R46" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6003,7 +6003,7 @@
         <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>98783</v>
+        <v>98789</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>103895</v>
+        <v>103901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661193</v>
+        <v>127661196</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>75130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>127661200</v>
       </c>
       <c r="B32" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>127660844</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661196</v>
+        <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>75127</v>
+        <v>80086</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4263,7 +4263,7 @@
         <v>127661184</v>
       </c>
       <c r="B35" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>127660831</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127660843</v>
+        <v>127661199</v>
       </c>
       <c r="B40" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R40" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4935,22 +4935,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127661199</v>
+        <v>127660843</v>
       </c>
       <c r="B41" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R41" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,12 +5052,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
         <v>127661194</v>
       </c>
       <c r="B42" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661203</v>
+        <v>127661202</v>
       </c>
       <c r="B43" t="n">
-        <v>79179</v>
+        <v>80127</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661202</v>
+        <v>127661203</v>
       </c>
       <c r="B44" t="n">
-        <v>80124</v>
+        <v>79182</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B45" t="n">
-        <v>75139</v>
+        <v>80127</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R45" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B46" t="n">
-        <v>80124</v>
+        <v>75142</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R46" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
         <v>127661197</v>
       </c>
       <c r="B47" t="n">
-        <v>79276</v>
+        <v>79279</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127660828</v>
       </c>
       <c r="B48" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>127660834</v>
       </c>
       <c r="B49" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>98789</v>
+        <v>98792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127661185</v>
+        <v>127660830</v>
       </c>
       <c r="B51" t="n">
-        <v>79101</v>
+        <v>75013</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>283</v>
+        <v>229654</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416559</v>
+        <v>416550</v>
       </c>
       <c r="R51" t="n">
-        <v>7047617</v>
+        <v>7047647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,60 +6191,60 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127660830</v>
+        <v>127661185</v>
       </c>
       <c r="B52" t="n">
-        <v>75010</v>
+        <v>79104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229654</v>
+        <v>283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416550</v>
+        <v>416559</v>
       </c>
       <c r="R52" t="n">
-        <v>7047647</v>
+        <v>7047617</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,82 +6308,73 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>80086</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R53" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6420,7 +6411,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6431,6 +6422,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6447,45 +6453,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B54" t="n">
-        <v>80083</v>
+        <v>57666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R54" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,7 +6537,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,21 +6548,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B55" t="n">
-        <v>98479</v>
+        <v>103904</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B56" t="n">
-        <v>103901</v>
+        <v>98482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
         <v>127660832</v>
       </c>
       <c r="B57" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,32 +3792,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661196</v>
+        <v>127661200</v>
       </c>
       <c r="B31" t="n">
-        <v>75130</v>
+        <v>80133</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661200</v>
+        <v>127660844</v>
       </c>
       <c r="B32" t="n">
-        <v>80127</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R32" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127660844</v>
+        <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>75136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R33" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,28 +4115,28 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
         <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>127661184</v>
       </c>
       <c r="B35" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105482</v>
+        <v>105490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B37" t="n">
-        <v>80161</v>
+        <v>80133</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R37" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B38" t="n">
-        <v>80127</v>
+        <v>80167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R38" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
         <v>127660831</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127661199</v>
+        <v>127660843</v>
       </c>
       <c r="B40" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R40" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4935,22 +4935,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127660843</v>
+        <v>127661199</v>
       </c>
       <c r="B41" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R41" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,44 +5052,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661194</v>
+        <v>127661202</v>
       </c>
       <c r="B42" t="n">
-        <v>80162</v>
+        <v>80133</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R42" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661202</v>
+        <v>127661203</v>
       </c>
       <c r="B43" t="n">
-        <v>80127</v>
+        <v>79188</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661203</v>
+        <v>127661194</v>
       </c>
       <c r="B44" t="n">
-        <v>79182</v>
+        <v>80168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R44" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5418,7 +5418,7 @@
         <v>127660842</v>
       </c>
       <c r="B45" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127661192</v>
       </c>
       <c r="B46" t="n">
-        <v>75142</v>
+        <v>75148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>127661197</v>
       </c>
       <c r="B47" t="n">
-        <v>79279</v>
+        <v>79285</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127660828</v>
       </c>
       <c r="B48" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>80126</v>
+        <v>98800</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R49" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,21 +5969,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6000,32 +5985,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B50" t="n">
-        <v>98792</v>
+        <v>80132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6035,10 +6020,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R50" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6075,7 +6060,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6086,6 +6071,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127660830</v>
+        <v>127661185</v>
       </c>
       <c r="B51" t="n">
-        <v>75013</v>
+        <v>79110</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229654</v>
+        <v>283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416550</v>
+        <v>416559</v>
       </c>
       <c r="R51" t="n">
-        <v>7047647</v>
+        <v>7047617</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,60 +6191,60 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127661185</v>
+        <v>127660830</v>
       </c>
       <c r="B52" t="n">
-        <v>79104</v>
+        <v>75019</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>283</v>
+        <v>229654</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416559</v>
+        <v>416550</v>
       </c>
       <c r="R52" t="n">
-        <v>7047617</v>
+        <v>7047647</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,73 +6308,82 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>80086</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R53" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6411,7 +6420,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,21 +6431,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6453,54 +6447,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B54" t="n">
-        <v>57666</v>
+        <v>80092</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R54" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6537,7 +6522,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6548,6 +6533,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>103904</v>
+        <v>98490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>98482</v>
+        <v>103912</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
         <v>127660832</v>
       </c>
       <c r="B57" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105490</v>
+        <v>105491</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80133</v>
+        <v>80167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R37" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80167</v>
+        <v>80133</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R38" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5886,7 +5886,7 @@
         <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>98800</v>
+        <v>98801</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6336,54 +6336,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>80092</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R53" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6420,7 +6411,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6431,6 +6422,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6447,45 +6453,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B54" t="n">
-        <v>80092</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R54" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,7 +6537,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,21 +6548,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B55" t="n">
-        <v>98490</v>
+        <v>103913</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B56" t="n">
-        <v>103912</v>
+        <v>98491</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,32 +3792,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661200</v>
+        <v>127661193</v>
       </c>
       <c r="B31" t="n">
-        <v>80133</v>
+        <v>80092</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3909,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R32" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661196</v>
+        <v>127660844</v>
       </c>
       <c r="B33" t="n">
-        <v>75136</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R33" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,38 +4115,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661193</v>
+        <v>127661196</v>
       </c>
       <c r="B34" t="n">
-        <v>80092</v>
+        <v>75136</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B37" t="n">
-        <v>80167</v>
+        <v>80133</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R37" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B38" t="n">
-        <v>80133</v>
+        <v>80167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R38" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>80133</v>
+        <v>75148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R45" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>75148</v>
+        <v>80133</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R46" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6336,45 +6336,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>80092</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R53" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6411,7 +6420,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,21 +6431,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6453,54 +6447,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>80092</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R54" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6537,7 +6522,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6548,6 +6533,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>103913</v>
+        <v>98491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,22 +6654,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>98491</v>
+        <v>103913</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
         <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6756,12 +6756,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105491</v>
+        <v>105492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661202</v>
+        <v>127661194</v>
       </c>
       <c r="B42" t="n">
-        <v>80133</v>
+        <v>80168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R42" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661203</v>
+        <v>127661202</v>
       </c>
       <c r="B43" t="n">
-        <v>79188</v>
+        <v>80133</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661194</v>
+        <v>127661203</v>
       </c>
       <c r="B44" t="n">
-        <v>80168</v>
+        <v>79188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R44" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B45" t="n">
-        <v>75148</v>
+        <v>80133</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R45" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B46" t="n">
-        <v>80133</v>
+        <v>75148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R46" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5886,7 +5886,7 @@
         <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>98801</v>
+        <v>98802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>103913</v>
+        <v>103914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3909,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661200</v>
+        <v>127660844</v>
       </c>
       <c r="B32" t="n">
-        <v>80133</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R32" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,38 +3998,38 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R33" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,28 +4115,28 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105492</v>
+        <v>105493</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B37" t="n">
-        <v>80133</v>
+        <v>80167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R37" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B38" t="n">
-        <v>80167</v>
+        <v>80133</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R38" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5064,32 +5064,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661194</v>
+        <v>127661203</v>
       </c>
       <c r="B42" t="n">
-        <v>80168</v>
+        <v>79188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R42" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661202</v>
+        <v>127661194</v>
       </c>
       <c r="B43" t="n">
-        <v>80133</v>
+        <v>80168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R43" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661203</v>
+        <v>127661202</v>
       </c>
       <c r="B44" t="n">
-        <v>79188</v>
+        <v>80133</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B49" t="n">
-        <v>98802</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R49" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,6 +5969,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5985,32 +6000,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B50" t="n">
-        <v>80132</v>
+        <v>98803</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6020,10 +6035,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R50" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6071,21 +6086,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6567,7 +6567,7 @@
         <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>127661187</v>
       </c>
       <c r="B56" t="n">
-        <v>103914</v>
+        <v>103915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,32 +3792,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661193</v>
+        <v>127660844</v>
       </c>
       <c r="B31" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R31" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,60 +3881,60 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127660844</v>
+        <v>127661193</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R32" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,60 +3998,60 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661200</v>
+        <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>80133</v>
+        <v>75136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,32 +4143,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661196</v>
+        <v>127661200</v>
       </c>
       <c r="B34" t="n">
-        <v>75136</v>
+        <v>80133</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4479,32 +4479,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127661195</v>
+        <v>127660829</v>
       </c>
       <c r="B37" t="n">
-        <v>80167</v>
+        <v>80133</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416497</v>
+        <v>416550</v>
       </c>
       <c r="R37" t="n">
-        <v>7047461</v>
+        <v>7047647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,44 +4584,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127660829</v>
+        <v>127661195</v>
       </c>
       <c r="B38" t="n">
-        <v>80133</v>
+        <v>80167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416550</v>
+        <v>416497</v>
       </c>
       <c r="R38" t="n">
-        <v>7047647</v>
+        <v>7047461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,12 +4701,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127660843</v>
+        <v>127661199</v>
       </c>
       <c r="B40" t="n">
         <v>80132</v>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R40" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4935,19 +4935,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127661199</v>
+        <v>127660843</v>
       </c>
       <c r="B41" t="n">
         <v>80132</v>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R41" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,12 +5052,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661194</v>
+        <v>127661202</v>
       </c>
       <c r="B43" t="n">
-        <v>80168</v>
+        <v>80133</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R43" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661202</v>
+        <v>127661194</v>
       </c>
       <c r="B44" t="n">
-        <v>80133</v>
+        <v>80168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R44" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127660842</v>
+        <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>80133</v>
+        <v>75148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R45" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127661192</v>
+        <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>75148</v>
+        <v>80133</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R46" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,12 +5637,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6336,54 +6336,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>80092</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R53" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6420,7 +6411,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6431,6 +6422,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6447,45 +6453,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B54" t="n">
-        <v>80092</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R54" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,7 +6537,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,21 +6548,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6336,45 +6336,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>80092</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R53" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6411,7 +6420,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,21 +6431,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6453,54 +6447,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>80092</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R54" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6537,7 +6522,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6548,6 +6533,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R31" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,38 +3881,38 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661193</v>
+        <v>127661196</v>
       </c>
       <c r="B32" t="n">
-        <v>80092</v>
+        <v>75136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4026,32 +4026,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661196</v>
+        <v>127660844</v>
       </c>
       <c r="B33" t="n">
-        <v>75136</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R33" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,60 +4115,60 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661200</v>
+        <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>80133</v>
+        <v>80092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661200</v>
+        <v>127660844</v>
       </c>
       <c r="B31" t="n">
-        <v>80133</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R31" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,38 +3881,38 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661196</v>
+        <v>127661193</v>
       </c>
       <c r="B32" t="n">
-        <v>75136</v>
+        <v>80092</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,21 +3920,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4026,32 +4026,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127660844</v>
+        <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>75136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R33" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,60 +4115,60 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661193</v>
+        <v>127661200</v>
       </c>
       <c r="B34" t="n">
-        <v>80092</v>
+        <v>80133</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6336,54 +6336,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660825</v>
+        <v>127660833</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>80092</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R53" t="n">
-        <v>7047696</v>
+        <v>7047565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6420,7 +6411,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6431,6 +6422,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6447,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660833</v>
+        <v>127660827</v>
       </c>
       <c r="B54" t="n">
-        <v>80092</v>
+        <v>98493</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,21 +6464,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6482,10 +6488,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R54" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,7 +6528,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,21 +6539,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6564,10 +6555,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127660827</v>
+        <v>127661187</v>
       </c>
       <c r="B55" t="n">
-        <v>98493</v>
+        <v>103915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,21 +6566,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6602,7 +6593,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047647</v>
+        <v>7047573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6639,7 +6630,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,44 +6645,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127661187</v>
+        <v>127660832</v>
       </c>
       <c r="B56" t="n">
-        <v>103915</v>
+        <v>80133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6701,10 +6692,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R56" t="n">
-        <v>7047573</v>
+        <v>7047565</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,7 +6732,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6752,26 +6743,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127660832</v>
+        <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>80133</v>
+        <v>57673</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,34 +6785,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R57" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6843,7 +6858,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6854,21 +6869,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127660844</v>
+        <v>127661200</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416391</v>
+        <v>416497</v>
       </c>
       <c r="R31" t="n">
-        <v>7047429</v>
+        <v>7047461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,60 +3881,60 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127661193</v>
+        <v>127660844</v>
       </c>
       <c r="B32" t="n">
-        <v>80092</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416497</v>
+        <v>416391</v>
       </c>
       <c r="R32" t="n">
-        <v>7047461</v>
+        <v>7047429</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,28 +3998,28 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
         <v>127661196</v>
       </c>
       <c r="B33" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,32 +4143,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661200</v>
+        <v>127661193</v>
       </c>
       <c r="B34" t="n">
-        <v>80133</v>
+        <v>80095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4263,7 +4263,7 @@
         <v>127661184</v>
       </c>
       <c r="B35" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>127660840</v>
       </c>
       <c r="B36" t="n">
-        <v>105493</v>
+        <v>105501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>127660829</v>
       </c>
       <c r="B37" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>127661195</v>
       </c>
       <c r="B38" t="n">
-        <v>80167</v>
+        <v>80170</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>127660831</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127661199</v>
+        <v>127660843</v>
       </c>
       <c r="B40" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416497</v>
+        <v>416538</v>
       </c>
       <c r="R40" t="n">
-        <v>7047461</v>
+        <v>7047463</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4935,22 +4935,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127660843</v>
+        <v>127661199</v>
       </c>
       <c r="B41" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416538</v>
+        <v>416497</v>
       </c>
       <c r="R41" t="n">
-        <v>7047463</v>
+        <v>7047461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,44 +5052,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661203</v>
+        <v>127661194</v>
       </c>
       <c r="B42" t="n">
-        <v>79188</v>
+        <v>80171</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416376</v>
+        <v>416497</v>
       </c>
       <c r="R42" t="n">
-        <v>7047411</v>
+        <v>7047461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5181,32 +5181,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661202</v>
+        <v>127661203</v>
       </c>
       <c r="B43" t="n">
-        <v>80133</v>
+        <v>79191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5270,17 +5270,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5298,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661194</v>
+        <v>127661202</v>
       </c>
       <c r="B44" t="n">
-        <v>80168</v>
+        <v>80136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416497</v>
+        <v>416376</v>
       </c>
       <c r="R44" t="n">
-        <v>7047461</v>
+        <v>7047411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5418,7 +5418,7 @@
         <v>127661192</v>
       </c>
       <c r="B45" t="n">
-        <v>75148</v>
+        <v>75151</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127660842</v>
       </c>
       <c r="B46" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>127661197</v>
       </c>
       <c r="B47" t="n">
-        <v>79285</v>
+        <v>79288</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>127660828</v>
       </c>
       <c r="B48" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,32 +5883,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660834</v>
+        <v>127660826</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>98811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R49" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,21 +5969,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6000,32 +5985,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660826</v>
+        <v>127660834</v>
       </c>
       <c r="B50" t="n">
-        <v>98803</v>
+        <v>80135</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6035,10 +6020,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416550</v>
+        <v>416538</v>
       </c>
       <c r="R50" t="n">
-        <v>7047647</v>
+        <v>7047565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6075,7 +6060,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6086,6 +6071,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127661185</v>
+        <v>127660830</v>
       </c>
       <c r="B51" t="n">
-        <v>79110</v>
+        <v>75022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>283</v>
+        <v>229654</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416559</v>
+        <v>416550</v>
       </c>
       <c r="R51" t="n">
-        <v>7047617</v>
+        <v>7047647</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,60 +6191,60 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127660830</v>
+        <v>127661185</v>
       </c>
       <c r="B52" t="n">
-        <v>75019</v>
+        <v>79113</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229654</v>
+        <v>283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416550</v>
+        <v>416559</v>
       </c>
       <c r="R52" t="n">
-        <v>7047647</v>
+        <v>7047617</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,28 +6308,28 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
         <v>127660833</v>
       </c>
       <c r="B53" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>127660827</v>
       </c>
       <c r="B54" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>127661187</v>
       </c>
       <c r="B55" t="n">
-        <v>103915</v>
+        <v>103923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>127660832</v>
       </c>
       <c r="B56" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6777,7 +6777,7 @@
         <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6777,7 +6777,7 @@
         <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6777,7 +6777,7 @@
         <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6777,7 +6777,7 @@
         <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -6777,7 +6777,7 @@
         <v>127660825</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89592718</v>
+        <v>127661185</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416527.8200128227</v>
+        <v>416559</v>
       </c>
       <c r="R2" t="n">
-        <v>7047463.978062761</v>
+        <v>7047617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,39 +762,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562387</v>
+        <v>127661192</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416169</v>
+        <v>416497</v>
       </c>
       <c r="R3" t="n">
-        <v>7047551</v>
+        <v>7047461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,17 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,66 +878,76 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562405</v>
+        <v>127661203</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416545</v>
+        <v>416376</v>
       </c>
       <c r="R4" t="n">
-        <v>7047634</v>
+        <v>7047411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,17 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,66 +995,76 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562397</v>
+        <v>127661204</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416318</v>
+        <v>416344</v>
       </c>
       <c r="R5" t="n">
-        <v>7047519</v>
+        <v>7047387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,17 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På gren på gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,31 +1112,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562401</v>
+        <v>127660829</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416440</v>
+        <v>416550</v>
       </c>
       <c r="R6" t="n">
-        <v>7047666</v>
+        <v>7047647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,17 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,31 +1229,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121562393</v>
+        <v>127660832</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,34 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416175</v>
+        <v>416538</v>
       </c>
       <c r="R7" t="n">
-        <v>7047616</v>
+        <v>7047565</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,17 +1325,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,31 +1346,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121562392</v>
+        <v>127660842</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416156</v>
+        <v>416538</v>
       </c>
       <c r="R8" t="n">
-        <v>7047605</v>
+        <v>7047463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,17 +1442,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,31 +1463,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121562382</v>
+        <v>127660846</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,34 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416431</v>
+        <v>416352</v>
       </c>
       <c r="R9" t="n">
-        <v>7047412</v>
+        <v>7047382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,17 +1559,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På bark på stam av levande gammal sälg (50 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,31 +1580,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121562398</v>
+        <v>127661184</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,34 +1622,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416421</v>
+        <v>416548</v>
       </c>
       <c r="R10" t="n">
-        <v>7047618</v>
+        <v>7047658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,17 +1676,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På grangren! Ej under asp! Gran ca 30 cm i diameter i gammal granskog, en död björk finns som kan ha fungerat som krondroppsträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,31 +1697,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121562407</v>
+        <v>127661200</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,34 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>416664</v>
+        <v>416497</v>
       </c>
       <c r="R11" t="n">
-        <v>7047789</v>
+        <v>7047461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,17 +1793,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,31 +1814,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121562406</v>
+        <v>127661202</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,34 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>416562</v>
+        <v>416376</v>
       </c>
       <c r="R12" t="n">
-        <v>7047700</v>
+        <v>7047411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,17 +1910,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,53 +1931,63 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121562403</v>
+        <v>89592692</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>416432</v>
+        <v>416564</v>
       </c>
       <c r="R13" t="n">
-        <v>7047696</v>
+        <v>7047506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,17 +2027,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,62 +2047,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121562385</v>
+        <v>127660831</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>416229</v>
+        <v>416545</v>
       </c>
       <c r="R14" t="n">
-        <v>7047508</v>
+        <v>7047606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,17 +2128,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Rikligt på gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,66 +2149,76 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121562394</v>
+        <v>127660844</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>416218</v>
+        <v>416391</v>
       </c>
       <c r="R15" t="n">
-        <v>7047582</v>
+        <v>7047429</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,17 +2245,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,66 +2266,76 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121562395</v>
+        <v>127661196</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>416317</v>
+        <v>416497</v>
       </c>
       <c r="R16" t="n">
-        <v>7047574</v>
+        <v>7047461</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,17 +2362,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,31 +2383,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121562388</v>
+        <v>89592718</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>416185</v>
+        <v>416528</v>
       </c>
       <c r="R17" t="n">
-        <v>7047533</v>
+        <v>7047464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,17 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,31 +2495,35 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121562381</v>
+        <v>127660828</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2531,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>416464</v>
+        <v>416550</v>
       </c>
       <c r="R18" t="n">
-        <v>7047388</v>
+        <v>7047647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,17 +2585,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,31 +2606,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562386</v>
+        <v>127660834</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,34 +2648,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>416228</v>
+        <v>416538</v>
       </c>
       <c r="R19" t="n">
-        <v>7047510</v>
+        <v>7047565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,17 +2702,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,31 +2723,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562400</v>
+        <v>127660843</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,34 +2765,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>416426</v>
+        <v>416538</v>
       </c>
       <c r="R20" t="n">
-        <v>7047612</v>
+        <v>7047463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,17 +2819,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,31 +2840,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562383</v>
+        <v>127661190</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,34 +2882,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>416419</v>
+        <v>416550</v>
       </c>
       <c r="R21" t="n">
-        <v>7047402</v>
+        <v>7047487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,17 +2936,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På levande sälg I gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,31 +2957,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562396</v>
+        <v>127661199</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,34 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>416304</v>
+        <v>416497</v>
       </c>
       <c r="R22" t="n">
-        <v>7047548</v>
+        <v>7047461</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,17 +3053,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,66 +3074,76 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562402</v>
+        <v>127661197</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>416433</v>
+        <v>416497</v>
       </c>
       <c r="R23" t="n">
-        <v>7047695</v>
+        <v>7047461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,17 +3170,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,66 +3191,76 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562389</v>
+        <v>127661195</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>416120</v>
+        <v>416497</v>
       </c>
       <c r="R24" t="n">
-        <v>7047580</v>
+        <v>7047461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,17 +3287,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,66 +3308,76 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562384</v>
+        <v>127661194</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pauten, Jmt</t>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>416263</v>
+        <v>416497</v>
       </c>
       <c r="R25" t="n">
-        <v>7047490</v>
+        <v>7047461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,17 +3404,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>På sälghögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3241,16 +3425,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3260,12 +3459,7 @@
         <v>121562379</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,15 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121562390</v>
+        <v>121562380</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>416139</v>
+        <v>416570</v>
       </c>
       <c r="R27" t="n">
-        <v>7047589</v>
+        <v>7047580</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,15 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121562391</v>
+        <v>121562381</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>416161</v>
+        <v>416464</v>
       </c>
       <c r="R28" t="n">
-        <v>7047590</v>
+        <v>7047388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,15 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121562380</v>
+        <v>121562382</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,10 +3797,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>416570</v>
+        <v>416431</v>
       </c>
       <c r="R29" t="n">
-        <v>7047580</v>
+        <v>7047412</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,15 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121562404</v>
+        <v>121562383</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>416533</v>
+        <v>416419</v>
       </c>
       <c r="R30" t="n">
-        <v>7047678</v>
+        <v>7047402</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127661200</v>
+        <v>121562384</v>
       </c>
       <c r="B31" t="n">
-        <v>80136</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,34 +3977,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>416497</v>
+        <v>416263</v>
       </c>
       <c r="R31" t="n">
-        <v>7047461</v>
+        <v>7047490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,17 +4031,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog. Där växer även lunglav, barkkornlav, gulnål, bårdlav,luddlav,korallblylav, nordlig nållav, Lecidea coriacea</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,41 +4052,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127660844</v>
+        <v>121562385</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,34 +4079,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>416391</v>
+        <v>416229</v>
       </c>
       <c r="R32" t="n">
-        <v>7047429</v>
+        <v>7047508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3974,17 +4133,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sparsamt på äldre gran i äldre granskog med högt inslag av glasbjörk</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,76 +4154,61 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127661196</v>
+        <v>121562386</v>
       </c>
       <c r="B33" t="n">
-        <v>75139</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>416497</v>
+        <v>416228</v>
       </c>
       <c r="R33" t="n">
-        <v>7047461</v>
+        <v>7047510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4091,17 +4235,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,76 +4256,61 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127661193</v>
+        <v>121562387</v>
       </c>
       <c r="B34" t="n">
-        <v>80095</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>416497</v>
+        <v>416169</v>
       </c>
       <c r="R34" t="n">
-        <v>7047461</v>
+        <v>7047551</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4208,17 +4337,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,41 +4358,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127661184</v>
+        <v>121562388</v>
       </c>
       <c r="B35" t="n">
-        <v>80136</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,34 +4385,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>416548</v>
+        <v>416185</v>
       </c>
       <c r="R35" t="n">
-        <v>7047658</v>
+        <v>7047533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,17 +4439,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På grangren! Ej under asp! Gran ca 30 cm i diameter i gammal granskog, en död björk finns som kan ha fungerat som krondroppsträd</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,76 +4460,61 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127660840</v>
+        <v>121562389</v>
       </c>
       <c r="B36" t="n">
-        <v>105501</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>416538</v>
+        <v>416120</v>
       </c>
       <c r="R36" t="n">
-        <v>7047463</v>
+        <v>7047580</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4442,17 +4541,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,22 +4566,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127660829</v>
+        <v>121562390</v>
       </c>
       <c r="B37" t="n">
-        <v>80136</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4490,34 +4589,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416550</v>
+        <v>416139</v>
       </c>
       <c r="R37" t="n">
-        <v>7047647</v>
+        <v>7047589</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4544,17 +4643,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4565,76 +4664,61 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127661195</v>
+        <v>121562391</v>
       </c>
       <c r="B38" t="n">
-        <v>80170</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416497</v>
+        <v>416161</v>
       </c>
       <c r="R38" t="n">
-        <v>7047461</v>
+        <v>7047590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,17 +4745,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4682,41 +4766,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127660831</v>
+        <v>121562392</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,34 +4793,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>416545</v>
+        <v>416156</v>
       </c>
       <c r="R39" t="n">
-        <v>7047606</v>
+        <v>7047605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,17 +4847,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4799,41 +4868,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127660843</v>
+        <v>121562393</v>
       </c>
       <c r="B40" t="n">
-        <v>80135</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,34 +4895,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416538</v>
+        <v>416175</v>
       </c>
       <c r="R40" t="n">
-        <v>7047463</v>
+        <v>7047616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,17 +4949,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog, även ögonpyrola på marken, samt skrovellav på sälgen</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4916,41 +4970,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127661199</v>
+        <v>121562394</v>
       </c>
       <c r="B41" t="n">
-        <v>80135</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,34 +4997,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416497</v>
+        <v>416218</v>
       </c>
       <c r="R41" t="n">
-        <v>7047461</v>
+        <v>7047582</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5012,17 +5051,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5033,76 +5072,61 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127661194</v>
+        <v>121562395</v>
       </c>
       <c r="B42" t="n">
-        <v>80171</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416497</v>
+        <v>416317</v>
       </c>
       <c r="R42" t="n">
-        <v>7047461</v>
+        <v>7047574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5129,17 +5153,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5150,76 +5174,61 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127661203</v>
+        <v>121562396</v>
       </c>
       <c r="B43" t="n">
-        <v>79191</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416376</v>
+        <v>416304</v>
       </c>
       <c r="R43" t="n">
-        <v>7047411</v>
+        <v>7047548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5246,17 +5255,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gren på gran i gammal granskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5267,41 +5276,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127661202</v>
+        <v>121562397</v>
       </c>
       <c r="B44" t="n">
-        <v>80136</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,34 +5303,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416376</v>
+        <v>416318</v>
       </c>
       <c r="R44" t="n">
-        <v>7047411</v>
+        <v>7047519</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,17 +5357,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5384,41 +5378,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127661192</v>
+        <v>121562398</v>
       </c>
       <c r="B45" t="n">
-        <v>75151</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5426,34 +5405,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416497</v>
+        <v>416421</v>
       </c>
       <c r="R45" t="n">
-        <v>7047461</v>
+        <v>7047618</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,17 +5459,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5501,41 +5480,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127660842</v>
+        <v>121562400</v>
       </c>
       <c r="B46" t="n">
-        <v>80136</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5543,34 +5507,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416538</v>
+        <v>416426</v>
       </c>
       <c r="R46" t="n">
-        <v>7047463</v>
+        <v>7047612</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,17 +5561,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5618,76 +5582,61 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127661197</v>
+        <v>121562401</v>
       </c>
       <c r="B47" t="n">
-        <v>79288</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>416497</v>
+        <v>416440</v>
       </c>
       <c r="R47" t="n">
-        <v>7047461</v>
+        <v>7047666</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5714,17 +5663,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På sälghögstubbe i gammal granskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5735,41 +5684,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127660828</v>
+        <v>121562402</v>
       </c>
       <c r="B48" t="n">
-        <v>80135</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,34 +5711,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>416550</v>
+        <v>416433</v>
       </c>
       <c r="R48" t="n">
-        <v>7047647</v>
+        <v>7047695</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5831,17 +5765,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5852,76 +5786,61 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127660826</v>
+        <v>121562403</v>
       </c>
       <c r="B49" t="n">
-        <v>98811</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416550</v>
+        <v>416432</v>
       </c>
       <c r="R49" t="n">
-        <v>7047647</v>
+        <v>7047696</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5948,17 +5867,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5973,22 +5892,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127660834</v>
+        <v>121562404</v>
       </c>
       <c r="B50" t="n">
-        <v>80135</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5996,34 +5915,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416538</v>
+        <v>416533</v>
       </c>
       <c r="R50" t="n">
-        <v>7047565</v>
+        <v>7047678</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6050,17 +5969,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog, även korallblylav och skrovellav</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6071,76 +5990,61 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127660830</v>
+        <v>121562405</v>
       </c>
       <c r="B51" t="n">
-        <v>75022</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229654</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416550</v>
+        <v>416545</v>
       </c>
       <c r="R51" t="n">
-        <v>7047647</v>
+        <v>7047634</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6167,17 +6071,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,41 +6092,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127661185</v>
+        <v>121562406</v>
       </c>
       <c r="B52" t="n">
-        <v>79113</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6230,34 +6119,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+          <t>Pauten, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416559</v>
+        <v>416562</v>
       </c>
       <c r="R52" t="n">
-        <v>7047617</v>
+        <v>7047700</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6284,17 +6173,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På kvist på levande gran ca 10 cm i diameter i glänta med mycket nordisk stormhatt, i gammal bördig granskog</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6305,76 +6194,70 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127660833</v>
+        <v>127660825</v>
       </c>
       <c r="B53" t="n">
-        <v>80095</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416538</v>
+        <v>416539</v>
       </c>
       <c r="R53" t="n">
-        <v>7047565</v>
+        <v>7047696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6411,7 +6294,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>1 lockande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,21 +6305,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6446,52 +6314,57 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127660827</v>
+        <v>127660845</v>
       </c>
       <c r="B54" t="n">
-        <v>98501</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416550</v>
+        <v>416362</v>
       </c>
       <c r="R54" t="n">
-        <v>7047647</v>
+        <v>7047385</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6528,7 +6401,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På marken i gammal gles ängsgranskog</t>
+          <t>Äldre ringhack på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6539,6 +6412,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6555,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127661187</v>
+        <v>127660827</v>
       </c>
       <c r="B55" t="n">
-        <v>103923</v>
+        <v>99142</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6566,21 +6454,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,7 +6481,7 @@
         <v>416550</v>
       </c>
       <c r="R55" t="n">
-        <v>7047573</v>
+        <v>7047647</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6630,7 +6518,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6645,7 +6533,7 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -6657,32 +6545,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127660832</v>
+        <v>127660826</v>
       </c>
       <c r="B56" t="n">
-        <v>80136</v>
+        <v>99456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6692,10 +6580,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>416538</v>
+        <v>416550</v>
       </c>
       <c r="R56" t="n">
-        <v>7047565</v>
+        <v>7047647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6732,7 +6620,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+          <t>På marken i gammal gles ängsgranskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6743,21 +6631,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6767,61 +6640,52 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127660825</v>
+        <v>127660840</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>106229</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>416539</v>
+        <v>416538</v>
       </c>
       <c r="R57" t="n">
-        <v>7047696</v>
+        <v>7047463</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6858,7 +6722,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1 lockande</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6882,6 +6746,775 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127661187</v>
+      </c>
+      <c r="B58" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7047573</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På marken i gammal bördig granskog även hässlebrodd</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127660833</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>416538</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7047565</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal rönn (30 cm dbh) i gammal ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127661193</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127660830</v>
+      </c>
+      <c r="B61" t="n">
+        <v>75356</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229654</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Plectocarpon scrobiculatae</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>416550</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7047647</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På skrovellav på bark på stam av levande gammal sälg (45 cm dbh) i gammal gles ängsgranskog, även skrovellav och lunglav, på marken rikligt med tvåblad, även kransrams</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127661191</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6008463</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cheiromycina petri</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D.Hawksw. &amp; Poelt</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Pauten, Kall, ca 9 km nordost Kall-Sölsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>416497</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7047461</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121562407</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>416664</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7047789</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121562408</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Pauten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>416681</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7047721</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49977-2024 artfynd.xlsx
+++ b/artfynd/A 49977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661203</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660829</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660832</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660842</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660846</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661184</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,6 +1892,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1959,6 +2014,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2060,6 +2120,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592692</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2177,6 +2242,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660831</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2294,6 +2364,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660844</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2411,6 +2486,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661196</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2517,6 +2597,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592718</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2634,6 +2719,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660828</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2751,6 +2841,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660834</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2868,6 +2963,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660843</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2985,6 +3085,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661190</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3102,6 +3207,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661199</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3219,6 +3329,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661197</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3336,6 +3451,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661195</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3453,6 +3573,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661194</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3555,6 +3680,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562379</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3657,6 +3787,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562380</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3759,6 +3894,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562381</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3861,6 +4001,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562382</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3963,6 +4108,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562383</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4065,6 +4215,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562384</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4167,6 +4322,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562385</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4269,6 +4429,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562386</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4371,6 +4536,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562387</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4473,6 +4643,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562388</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4575,6 +4750,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562389</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4677,6 +4857,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562390</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4779,6 +4964,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562391</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4881,6 +5071,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562392</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4983,6 +5178,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562393</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5085,6 +5285,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562394</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5187,6 +5392,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562395</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5289,6 +5499,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562396</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5391,6 +5606,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562397</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5493,6 +5713,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562398</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5595,6 +5820,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562400</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5697,6 +5927,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562401</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5799,6 +6034,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562402</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5901,6 +6141,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562403</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6003,6 +6248,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562404</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6105,6 +6355,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562405</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6207,6 +6462,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562406</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6309,6 +6569,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562407</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6411,6 +6676,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121562408</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6522,6 +6792,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660825</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6644,6 +6919,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660845</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6746,6 +7026,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660827</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6848,6 +7133,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660826</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6950,6 +7240,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660840</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7052,6 +7347,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661187</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7169,6 +7469,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660833</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7286,6 +7591,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661193</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7403,6 +7713,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127660830</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7515,8 +7830,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127661191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>